--- a/Eventy requirements assignee - Submission.xlsx
+++ b/Eventy requirements assignee - Submission.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joman\Desktop\Eventy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E7991F9-6070-4C28-92F1-4BA1E90550C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A515B7B-8300-4F19-8EA8-B82094912940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="162">
   <si>
     <t xml:space="preserve">As a </t>
   </si>
@@ -542,6 +542,9 @@
   </si>
   <si>
     <t>create conferences by adding the conference name, start and end dates and times, short description, full agenda, conference website link, required budget, source of funding (extrernal or GUC), extra required resources</t>
+  </si>
+  <si>
+    <t>Walid</t>
   </si>
 </sst>
 </file>
@@ -692,14 +695,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -709,9 +707,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -739,11 +734,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -774,6 +764,30 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -989,7 +1003,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y1000"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1007,3609 +1020,3887 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25"/>
-      <c r="B1" s="26" t="s">
+      <c r="A1" s="18"/>
+      <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28">
+      <c r="A2" s="21">
         <v>1</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="30" t="s">
+      <c r="D2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="32">
         <v>2.5</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="32">
         <v>1</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4"/>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
     </row>
     <row r="3" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28">
-        <v>2</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="21">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="7">
-        <v>2</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="D3" s="23"/>
+      <c r="E3" s="32">
+        <v>2</v>
+      </c>
+      <c r="F3" s="32">
         <v>1</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
-      <c r="V3" s="7"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
-      <c r="Y3" s="7"/>
-    </row>
-    <row r="4" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+    </row>
+    <row r="4" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="7"/>
-      <c r="S4" s="7"/>
-      <c r="T4" s="7"/>
-      <c r="U4" s="7"/>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
-      <c r="Y4" s="7"/>
-    </row>
-    <row r="5" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32">
+        <v>2</v>
+      </c>
+      <c r="F4" s="32">
+        <v>2</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+    </row>
+    <row r="5" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="7">
-        <v>2</v>
-      </c>
-      <c r="F5" s="7">
-        <v>2</v>
-      </c>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
-      <c r="T5" s="7"/>
-      <c r="U5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
-      <c r="Y5" s="7"/>
+      <c r="E5" s="32">
+        <v>2</v>
+      </c>
+      <c r="F5" s="32">
+        <v>2</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
     </row>
     <row r="6" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28">
+      <c r="A6" s="21">
         <v>5</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="30"/>
-      <c r="E6" s="7">
-        <v>2</v>
-      </c>
-      <c r="F6" s="7">
+      <c r="D6" s="23"/>
+      <c r="E6" s="32">
+        <v>2</v>
+      </c>
+      <c r="F6" s="32">
         <v>1</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7"/>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
     </row>
     <row r="7" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="32">
         <v>3</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="32">
         <v>1</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
-      <c r="S7" s="7"/>
-      <c r="T7" s="7"/>
-      <c r="U7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="X7" s="7"/>
-      <c r="Y7" s="7"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
     </row>
     <row r="8" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28">
+      <c r="A8" s="21">
         <v>7</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="30"/>
-      <c r="E8" s="7">
-        <v>2</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="D8" s="23"/>
+      <c r="E8" s="32">
+        <v>2</v>
+      </c>
+      <c r="F8" s="32">
         <v>1</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7"/>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
     </row>
     <row r="9" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="28">
+      <c r="A9" s="21">
         <v>8</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="7">
-        <v>2</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="D9" s="23"/>
+      <c r="E9" s="32">
+        <v>2</v>
+      </c>
+      <c r="F9" s="32">
         <v>1</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-      <c r="U9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
     </row>
     <row r="10" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="28">
+      <c r="A10" s="21">
         <v>9</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="32">
         <v>3</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="32">
         <v>1</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
     </row>
     <row r="11" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="28">
+      <c r="A11" s="21">
         <v>10</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="30"/>
-      <c r="E11" s="7">
+      <c r="D11" s="23"/>
+      <c r="E11" s="32">
         <v>3</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="32">
         <v>1</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="X11" s="7"/>
-      <c r="Y11" s="7"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
     </row>
     <row r="12" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28">
+      <c r="A12" s="21">
         <v>11</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="32">
         <v>3</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="32">
         <v>1</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7"/>
-      <c r="R12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="T12" s="7"/>
-      <c r="U12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="X12" s="7"/>
-      <c r="Y12" s="7"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
     </row>
     <row r="13" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28">
+      <c r="A13" s="21">
         <v>12</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="30"/>
-      <c r="E13" s="7">
+      <c r="D13" s="23"/>
+      <c r="E13" s="32">
         <v>3</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="32">
         <v>1</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-    </row>
-    <row r="14" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4">
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+    </row>
+    <row r="14" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7">
+      <c r="D14" s="23"/>
+      <c r="E14" s="32">
         <v>3</v>
       </c>
-      <c r="F14" s="7">
-        <v>2</v>
-      </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
-      <c r="U14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="X14" s="7"/>
-      <c r="Y14" s="7"/>
-    </row>
-    <row r="15" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4">
+      <c r="F14" s="32">
+        <v>2</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+    </row>
+    <row r="15" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="21">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7">
+      <c r="D15" s="23"/>
+      <c r="E15" s="32">
         <v>3</v>
       </c>
-      <c r="F15" s="7">
-        <v>2</v>
-      </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
-      <c r="U15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="X15" s="7"/>
-      <c r="Y15" s="7"/>
-    </row>
-    <row r="16" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4">
+      <c r="F15" s="32">
+        <v>2</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+    </row>
+    <row r="16" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21">
         <v>15</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7">
-        <v>2</v>
-      </c>
-      <c r="F16" s="7">
-        <v>2</v>
-      </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-      <c r="U16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="X16" s="7"/>
-      <c r="Y16" s="7"/>
-    </row>
-    <row r="17" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4">
+      <c r="D16" s="23"/>
+      <c r="E16" s="32">
+        <v>2</v>
+      </c>
+      <c r="F16" s="32">
+        <v>2</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+    </row>
+    <row r="17" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="21">
         <v>16</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7">
-        <v>2</v>
-      </c>
-      <c r="F17" s="7">
-        <v>2</v>
-      </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
-      <c r="U17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="X17" s="7"/>
-      <c r="Y17" s="7"/>
-    </row>
-    <row r="18" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4">
+      <c r="D17" s="23"/>
+      <c r="E17" s="32">
+        <v>2</v>
+      </c>
+      <c r="F17" s="32">
+        <v>2</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+    </row>
+    <row r="18" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7">
+      <c r="D18" s="23"/>
+      <c r="E18" s="32">
         <v>3</v>
       </c>
-      <c r="F18" s="7">
-        <v>2</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
-      <c r="U18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="X18" s="7"/>
-      <c r="Y18" s="7"/>
-    </row>
-    <row r="19" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4">
+      <c r="F18" s="32">
+        <v>2</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H18" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+    </row>
+    <row r="19" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="21">
         <v>18</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="7">
-        <v>2</v>
-      </c>
-      <c r="F19" s="7">
-        <v>2</v>
-      </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
-      <c r="U19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="X19" s="7"/>
-      <c r="Y19" s="7"/>
-    </row>
-    <row r="20" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4">
+      <c r="D19" s="23"/>
+      <c r="E19" s="32">
+        <v>2</v>
+      </c>
+      <c r="F19" s="32">
+        <v>2</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+    </row>
+    <row r="20" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="7">
-        <v>2</v>
-      </c>
-      <c r="F20" s="7">
-        <v>2</v>
-      </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
-      <c r="U20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="X20" s="7"/>
-      <c r="Y20" s="7"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="32">
+        <v>2</v>
+      </c>
+      <c r="F20" s="32">
+        <v>2</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
     </row>
     <row r="21" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="28">
+      <c r="A21" s="21">
         <v>20</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="7">
+      <c r="D21" s="23"/>
+      <c r="E21" s="32">
         <v>4</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="32">
         <v>1</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-    </row>
-    <row r="22" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="4">
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+    </row>
+    <row r="22" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21">
         <v>21</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="7">
+      <c r="D22" s="23"/>
+      <c r="E22" s="32">
         <v>5</v>
       </c>
-      <c r="F22" s="7">
-        <v>2</v>
-      </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
-      <c r="U22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="X22" s="7"/>
-      <c r="Y22" s="7"/>
-    </row>
-    <row r="23" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4">
+      <c r="F22" s="32">
+        <v>2</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+    </row>
+    <row r="23" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21">
         <v>22</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="6"/>
-      <c r="E23" s="7">
+      <c r="D23" s="23"/>
+      <c r="E23" s="32">
         <v>4</v>
       </c>
-      <c r="F23" s="7">
-        <v>2</v>
-      </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="7"/>
-      <c r="U23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="X23" s="7"/>
-      <c r="Y23" s="7"/>
-    </row>
-    <row r="24" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4">
+      <c r="F23" s="32">
+        <v>2</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+    </row>
+    <row r="24" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21">
         <v>23</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="7">
+      <c r="D24" s="23"/>
+      <c r="E24" s="32">
         <v>4</v>
       </c>
-      <c r="F24" s="7">
-        <v>2</v>
-      </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
-      <c r="U24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="X24" s="7"/>
-      <c r="Y24" s="7"/>
+      <c r="F24" s="32">
+        <v>2</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
     </row>
     <row r="25" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="28">
+      <c r="A25" s="21">
         <v>24</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="30"/>
-      <c r="E25" s="7">
+      <c r="D25" s="23"/>
+      <c r="E25" s="32">
         <v>4</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="32">
         <v>1</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="X25" s="7"/>
-      <c r="Y25" s="7"/>
-    </row>
-    <row r="26" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4">
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+    </row>
+    <row r="26" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21">
         <v>25</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="7">
+      <c r="D26" s="23"/>
+      <c r="E26" s="32">
         <v>4</v>
       </c>
-      <c r="F26" s="7">
-        <v>2</v>
-      </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="X26" s="7"/>
-      <c r="Y26" s="7"/>
-    </row>
-    <row r="27" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4">
+      <c r="F26" s="32">
+        <v>2</v>
+      </c>
+      <c r="G26" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+    </row>
+    <row r="27" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="21">
         <v>26</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="6"/>
-      <c r="E27" s="7">
+      <c r="D27" s="23"/>
+      <c r="E27" s="32">
         <v>4</v>
       </c>
-      <c r="F27" s="7">
-        <v>2</v>
-      </c>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="X27" s="7"/>
-      <c r="Y27" s="7"/>
+      <c r="F27" s="32">
+        <v>2</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
     </row>
     <row r="28" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="28">
+      <c r="A28" s="21">
         <v>27</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="30" t="s">
+      <c r="D28" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="34">
         <v>4</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="34">
         <v>1</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="Q28" s="9"/>
-      <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-    </row>
-    <row r="29" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4">
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="5"/>
+      <c r="U28" s="5"/>
+      <c r="V28" s="5"/>
+      <c r="W28" s="5"/>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+    </row>
+    <row r="29" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="21">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="32">
         <v>4</v>
       </c>
-      <c r="F29" s="7">
-        <v>2</v>
-      </c>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
-      <c r="U29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="X29" s="7"/>
-      <c r="Y29" s="7"/>
-    </row>
-    <row r="30" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4">
+      <c r="F29" s="32">
+        <v>2</v>
+      </c>
+      <c r="G29" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+    </row>
+    <row r="30" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21">
         <v>29</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="7">
+      <c r="D30" s="23"/>
+      <c r="E30" s="32">
         <v>4</v>
       </c>
-      <c r="F30" s="7">
-        <v>2</v>
-      </c>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
-      <c r="U30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="X30" s="7"/>
-      <c r="Y30" s="7"/>
-    </row>
-    <row r="31" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4">
+      <c r="F30" s="32">
+        <v>2</v>
+      </c>
+      <c r="G30" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+    </row>
+    <row r="31" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21">
         <v>30</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="7">
+      <c r="D31" s="23"/>
+      <c r="E31" s="32">
         <v>4</v>
       </c>
-      <c r="F31" s="7">
-        <v>2</v>
-      </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
-      <c r="U31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="X31" s="7"/>
-      <c r="Y31" s="7"/>
+      <c r="F31" s="32">
+        <v>2</v>
+      </c>
+      <c r="G31" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H31" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
     </row>
     <row r="32" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="28">
+      <c r="A32" s="21">
         <v>31</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="30"/>
-      <c r="E32" s="2">
-        <v>2</v>
-      </c>
-      <c r="F32" s="2">
+      <c r="D32" s="23"/>
+      <c r="E32" s="30">
+        <v>2</v>
+      </c>
+      <c r="F32" s="30">
         <v>1</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="H32" s="31" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="28">
+      <c r="A33" s="21">
         <v>32</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="D33" s="30" t="s">
+      <c r="D33" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="E33" s="2">
-        <v>2</v>
-      </c>
-      <c r="F33" s="2">
+      <c r="E33" s="30">
+        <v>2</v>
+      </c>
+      <c r="F33" s="30">
         <v>1</v>
       </c>
-      <c r="G33" s="3" t="s">
+      <c r="G33" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="H33" s="31" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="28">
+      <c r="A34" s="21">
         <v>33</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D34" s="30"/>
-      <c r="E34" s="2">
-        <v>2</v>
-      </c>
-      <c r="F34" s="2">
+      <c r="D34" s="23"/>
+      <c r="E34" s="30">
+        <v>2</v>
+      </c>
+      <c r="F34" s="30">
         <v>1</v>
       </c>
-      <c r="G34" s="3" t="s">
+      <c r="G34" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="28">
+      <c r="A35" s="21">
         <v>34</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="30" t="s">
+      <c r="D35" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="2">
-        <v>2</v>
-      </c>
-      <c r="F35" s="2">
+      <c r="E35" s="30">
+        <v>2</v>
+      </c>
+      <c r="F35" s="30">
         <v>1</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="H35" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="28">
+      <c r="A36" s="21">
         <v>35</v>
       </c>
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D36" s="30"/>
-      <c r="E36" s="2">
-        <v>2</v>
-      </c>
-      <c r="F36" s="2">
+      <c r="D36" s="23"/>
+      <c r="E36" s="30">
+        <v>2</v>
+      </c>
+      <c r="F36" s="30">
         <v>1</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="31" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="28">
+      <c r="A37" s="21">
         <v>36</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D37" s="30"/>
-      <c r="E37" s="2">
-        <v>2</v>
-      </c>
-      <c r="F37" s="2">
+      <c r="D37" s="23"/>
+      <c r="E37" s="30">
+        <v>2</v>
+      </c>
+      <c r="F37" s="30">
         <v>1</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H37" s="31" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="28">
+      <c r="A38" s="21">
         <v>37</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="30"/>
-      <c r="E38" s="2">
-        <v>2</v>
-      </c>
-      <c r="F38" s="2">
+      <c r="D38" s="23"/>
+      <c r="E38" s="30">
+        <v>2</v>
+      </c>
+      <c r="F38" s="30">
         <v>1</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H38" s="31" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+    <row r="39" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="21">
         <v>38</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="2">
-        <v>2</v>
-      </c>
-      <c r="F39" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="D39" s="23"/>
+      <c r="E39" s="30">
+        <v>2</v>
+      </c>
+      <c r="F39" s="32">
+        <v>2</v>
+      </c>
+      <c r="G39" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H39" s="30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="21">
         <v>39</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="D40" s="6"/>
-      <c r="E40" s="2">
-        <v>2</v>
-      </c>
-      <c r="F40" s="7">
-        <v>2</v>
+      <c r="D40" s="23"/>
+      <c r="E40" s="30">
+        <v>2</v>
+      </c>
+      <c r="F40" s="32">
+        <v>2</v>
+      </c>
+      <c r="G40" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H40" s="30" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="28">
+      <c r="A41" s="21">
         <v>40</v>
       </c>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D41" s="30"/>
-      <c r="E41" s="2">
-        <v>2</v>
-      </c>
-      <c r="F41" s="2">
+      <c r="D41" s="23"/>
+      <c r="E41" s="30">
+        <v>2</v>
+      </c>
+      <c r="F41" s="30">
         <v>1</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="28">
+      <c r="A42" s="21">
         <v>41</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="D42" s="30"/>
-      <c r="E42" s="2">
-        <v>2</v>
-      </c>
-      <c r="F42" s="2">
+      <c r="D42" s="23"/>
+      <c r="E42" s="30">
+        <v>2</v>
+      </c>
+      <c r="F42" s="30">
         <v>1</v>
       </c>
-      <c r="G42" s="3" t="s">
+      <c r="G42" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="H42" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="28">
+      <c r="A43" s="21">
         <v>42</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="30"/>
-      <c r="E43" s="2">
-        <v>2</v>
-      </c>
-      <c r="F43" s="2">
+      <c r="D43" s="23"/>
+      <c r="E43" s="30">
+        <v>2</v>
+      </c>
+      <c r="F43" s="30">
         <v>1</v>
       </c>
-      <c r="G43" s="3" t="s">
+      <c r="G43" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="H43" s="31" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4">
+    <row r="44" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="21">
         <v>43</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="6"/>
-      <c r="E44" s="2">
-        <v>2</v>
-      </c>
-      <c r="F44" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
+      <c r="D44" s="23"/>
+      <c r="E44" s="30">
+        <v>2</v>
+      </c>
+      <c r="F44" s="32">
+        <v>2</v>
+      </c>
+      <c r="G44" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="H44" s="30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="21">
         <v>44</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="D45" s="6"/>
-      <c r="E45" s="2">
-        <v>2</v>
-      </c>
-      <c r="F45" s="7">
-        <v>2</v>
+      <c r="D45" s="23"/>
+      <c r="E45" s="30">
+        <v>2</v>
+      </c>
+      <c r="F45" s="32">
+        <v>2</v>
+      </c>
+      <c r="G45" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="30" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="28">
+      <c r="A46" s="21">
         <v>45</v>
       </c>
-      <c r="B46" s="32" t="s">
+      <c r="B46" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="30" t="s">
+      <c r="D46" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="E46" s="9">
-        <v>2</v>
-      </c>
-      <c r="F46" s="9">
+      <c r="E46" s="34">
+        <v>2</v>
+      </c>
+      <c r="F46" s="34">
         <v>1</v>
       </c>
-      <c r="G46" s="9" t="s">
+      <c r="G46" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="9"/>
-      <c r="R46" s="9"/>
-      <c r="S46" s="9"/>
-      <c r="T46" s="9"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
-      <c r="Y46" s="9"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
     </row>
     <row r="47" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="28">
+      <c r="A47" s="21">
         <v>46</v>
       </c>
-      <c r="B47" s="29" t="s">
+      <c r="B47" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="D47" s="30"/>
-      <c r="E47" s="2">
-        <v>2</v>
-      </c>
-      <c r="F47" s="2">
+      <c r="D47" s="23"/>
+      <c r="E47" s="30">
+        <v>2</v>
+      </c>
+      <c r="F47" s="30">
         <v>1</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="H47" s="31" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4">
+    <row r="48" spans="1:25" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="21">
         <v>47</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="E48" s="2">
-        <v>2</v>
-      </c>
-      <c r="F48" s="7">
-        <v>2</v>
+      <c r="E48" s="30">
+        <v>2</v>
+      </c>
+      <c r="F48" s="32">
+        <v>2</v>
+      </c>
+      <c r="G48" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="30" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="28">
+      <c r="A49" s="21">
         <v>48</v>
       </c>
-      <c r="B49" s="29" t="s">
+      <c r="B49" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D49" s="30" t="s">
+      <c r="D49" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="E49" s="2">
-        <v>2</v>
-      </c>
-      <c r="F49" s="2">
+      <c r="E49" s="30">
+        <v>2</v>
+      </c>
+      <c r="F49" s="30">
         <v>1</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H49" s="31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4">
+    <row r="50" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="21">
         <v>49</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="D50" s="6"/>
-      <c r="E50" s="2">
-        <v>2</v>
-      </c>
-      <c r="F50" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="4">
+      <c r="D50" s="23"/>
+      <c r="E50" s="30">
+        <v>2</v>
+      </c>
+      <c r="F50" s="32">
+        <v>2</v>
+      </c>
+      <c r="G50" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="21">
         <v>50</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="E51" s="2">
-        <v>2</v>
-      </c>
-      <c r="F51" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4">
+      <c r="E51" s="30">
+        <v>2</v>
+      </c>
+      <c r="F51" s="32">
+        <v>2</v>
+      </c>
+      <c r="G51" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H51" s="30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="21">
         <v>51</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="D52" s="6"/>
-      <c r="E52" s="2">
-        <v>2</v>
-      </c>
-      <c r="F52" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="4">
+      <c r="D52" s="23"/>
+      <c r="E52" s="30">
+        <v>2</v>
+      </c>
+      <c r="F52" s="32">
+        <v>2</v>
+      </c>
+      <c r="G52" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H52" s="30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="21">
         <v>52</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="D53" s="6"/>
-      <c r="E53" s="2">
-        <v>2</v>
-      </c>
-      <c r="F53" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="4">
+      <c r="D53" s="23"/>
+      <c r="E53" s="30">
+        <v>2</v>
+      </c>
+      <c r="F53" s="32">
+        <v>2</v>
+      </c>
+      <c r="G53" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="21">
         <v>53</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="6"/>
-      <c r="E54" s="2">
-        <v>2</v>
-      </c>
-      <c r="F54" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4">
+      <c r="D54" s="23"/>
+      <c r="E54" s="30">
+        <v>2</v>
+      </c>
+      <c r="F54" s="32">
+        <v>2</v>
+      </c>
+      <c r="G54" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="21">
         <v>54</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="D55" s="6"/>
-      <c r="E55" s="2">
-        <v>2</v>
-      </c>
-      <c r="F55" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="4">
+      <c r="D55" s="23"/>
+      <c r="E55" s="30">
+        <v>2</v>
+      </c>
+      <c r="F55" s="32">
+        <v>2</v>
+      </c>
+      <c r="G55" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H55" s="30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="21">
         <v>55</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D56" s="6"/>
-      <c r="E56" s="2">
-        <v>2</v>
-      </c>
-      <c r="F56" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="4">
+      <c r="D56" s="23"/>
+      <c r="E56" s="30">
+        <v>2</v>
+      </c>
+      <c r="F56" s="32">
+        <v>2</v>
+      </c>
+      <c r="G56" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H56" s="30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="21">
         <v>56</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="D57" s="6"/>
-      <c r="E57" s="2">
-        <v>2</v>
-      </c>
-      <c r="F57" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4">
+      <c r="D57" s="23"/>
+      <c r="E57" s="30">
+        <v>2</v>
+      </c>
+      <c r="F57" s="32">
+        <v>2</v>
+      </c>
+      <c r="G57" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57" s="30" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="21">
         <v>57</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="D58" s="6"/>
-      <c r="E58" s="2">
+      <c r="D58" s="23"/>
+      <c r="E58" s="30">
         <v>5</v>
       </c>
-      <c r="F58" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="4">
+      <c r="F58" s="32">
+        <v>2</v>
+      </c>
+      <c r="G58" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H58" s="30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="21">
         <v>58</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="D59" s="6"/>
-      <c r="E59" s="2">
+      <c r="D59" s="23"/>
+      <c r="E59" s="30">
         <v>5</v>
       </c>
-      <c r="F59" s="7">
-        <v>2</v>
+      <c r="F59" s="32">
+        <v>2</v>
+      </c>
+      <c r="G59" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H59" s="30" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="28">
+      <c r="A60" s="21">
         <v>59</v>
       </c>
-      <c r="B60" s="29" t="s">
+      <c r="B60" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="D60" s="27"/>
-      <c r="E60" s="2">
-        <v>2</v>
-      </c>
-      <c r="F60" s="2">
+      <c r="D60" s="20"/>
+      <c r="E60" s="30">
+        <v>2</v>
+      </c>
+      <c r="F60" s="30">
         <v>1</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="H60" s="31" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="28">
+      <c r="A61" s="21">
         <v>60</v>
       </c>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="D61" s="30" t="s">
+      <c r="D61" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E61" s="2">
-        <v>2</v>
-      </c>
-      <c r="F61" s="2">
+      <c r="E61" s="30">
+        <v>2</v>
+      </c>
+      <c r="F61" s="30">
         <v>1</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="H61" s="31" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="28">
+      <c r="A62" s="21">
         <v>61</v>
       </c>
-      <c r="B62" s="33" t="s">
+      <c r="B62" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="33" t="s">
+      <c r="C62" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="D62" s="30" t="s">
+      <c r="D62" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="E62" s="2">
-        <v>2</v>
-      </c>
-      <c r="F62" s="2">
+      <c r="E62" s="30">
+        <v>2</v>
+      </c>
+      <c r="F62" s="30">
         <v>1</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H62" s="31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="4">
+    <row r="63" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="21">
         <v>62</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="2">
-        <v>2</v>
-      </c>
-      <c r="F63" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="4">
+      <c r="D63" s="23"/>
+      <c r="E63" s="30">
+        <v>2</v>
+      </c>
+      <c r="F63" s="32">
+        <v>2</v>
+      </c>
+      <c r="G63" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H63" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="21">
         <v>63</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="D64" s="6"/>
-      <c r="E64" s="2">
-        <v>2</v>
-      </c>
-      <c r="F64" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="4">
+      <c r="D64" s="23"/>
+      <c r="E64" s="30">
+        <v>2</v>
+      </c>
+      <c r="F64" s="32">
+        <v>2</v>
+      </c>
+      <c r="G64" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="H64" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="21">
+        <v>64</v>
+      </c>
+      <c r="B65" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="E65" s="2">
-        <v>2</v>
-      </c>
-      <c r="F65" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="4">
+      <c r="E65" s="30">
+        <v>2</v>
+      </c>
+      <c r="F65" s="32">
+        <v>2</v>
+      </c>
+      <c r="G65" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H65" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="21">
         <v>65</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D66" s="6"/>
-      <c r="E66" s="2">
-        <v>2</v>
-      </c>
-      <c r="F66" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="4">
+      <c r="D66" s="23"/>
+      <c r="E66" s="30">
+        <v>2</v>
+      </c>
+      <c r="F66" s="32">
+        <v>2</v>
+      </c>
+      <c r="G66" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H66" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="21">
         <v>66</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B67" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="D67" s="6"/>
-      <c r="E67" s="2">
-        <v>2</v>
-      </c>
-      <c r="F67" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="4">
+      <c r="D67" s="23"/>
+      <c r="E67" s="30">
+        <v>2</v>
+      </c>
+      <c r="F67" s="32">
+        <v>2</v>
+      </c>
+      <c r="G67" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H67" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="21">
         <v>67</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="E68" s="2">
-        <v>2</v>
-      </c>
-      <c r="F68" s="7">
-        <v>2</v>
+      <c r="E68" s="30">
+        <v>2</v>
+      </c>
+      <c r="F68" s="32">
+        <v>2</v>
+      </c>
+      <c r="G68" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H68" s="30" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="28">
+      <c r="A69" s="21">
         <v>68</v>
       </c>
-      <c r="B69" s="34" t="s">
+      <c r="B69" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="C69" s="33" t="s">
+      <c r="C69" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="D69" s="30"/>
-      <c r="E69" s="2">
-        <v>2</v>
-      </c>
-      <c r="F69" s="2">
+      <c r="D69" s="23"/>
+      <c r="E69" s="30">
+        <v>2</v>
+      </c>
+      <c r="F69" s="30">
         <v>1</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="G69" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="H69" s="31" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="28">
+      <c r="A70" s="21">
         <v>69</v>
       </c>
-      <c r="B70" s="33" t="s">
+      <c r="B70" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C70" s="33" t="s">
+      <c r="C70" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="D70" s="30"/>
-      <c r="E70" s="2">
-        <v>2</v>
-      </c>
-      <c r="F70" s="2">
+      <c r="D70" s="23"/>
+      <c r="E70" s="30">
+        <v>2</v>
+      </c>
+      <c r="F70" s="30">
         <v>1</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="G70" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="H70" s="31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="4">
+    <row r="71" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="21">
         <v>70</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="D71" s="6"/>
-      <c r="E71" s="2">
-        <v>2</v>
-      </c>
-      <c r="F71" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4">
+      <c r="D71" s="23"/>
+      <c r="E71" s="30">
+        <v>2</v>
+      </c>
+      <c r="F71" s="32">
+        <v>2</v>
+      </c>
+      <c r="G71" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H71" s="30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="21">
         <v>71</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="D72" s="6"/>
-      <c r="E72" s="2">
-        <v>2</v>
-      </c>
-      <c r="F72" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="4">
+      <c r="D72" s="23"/>
+      <c r="E72" s="30">
+        <v>2</v>
+      </c>
+      <c r="F72" s="32">
+        <v>2</v>
+      </c>
+      <c r="G72" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H72" s="30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="21">
         <v>72</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="D73" s="6"/>
-      <c r="E73" s="2">
+      <c r="D73" s="23"/>
+      <c r="E73" s="30">
         <v>4</v>
       </c>
-      <c r="F73" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="4">
+      <c r="F73" s="32">
+        <v>2</v>
+      </c>
+      <c r="G73" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H73" s="30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="21">
         <v>73</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="6"/>
-      <c r="E74" s="2">
+      <c r="D74" s="23"/>
+      <c r="E74" s="30">
         <v>4</v>
       </c>
-      <c r="F74" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4">
+      <c r="F74" s="32">
+        <v>2</v>
+      </c>
+      <c r="G74" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74" s="30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="21">
         <v>74</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="6"/>
-      <c r="E75" s="2">
-        <v>2</v>
-      </c>
-      <c r="F75" s="7">
-        <v>2</v>
+      <c r="D75" s="23"/>
+      <c r="E75" s="30">
+        <v>2</v>
+      </c>
+      <c r="F75" s="32">
+        <v>2</v>
+      </c>
+      <c r="G75" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="H75" s="30" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="28">
+      <c r="A76" s="21">
         <v>75</v>
       </c>
-      <c r="B76" s="33" t="s">
+      <c r="B76" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C76" s="33" t="s">
+      <c r="C76" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="D76" s="30"/>
-      <c r="E76" s="2">
-        <v>2</v>
-      </c>
-      <c r="F76" s="2">
+      <c r="D76" s="23"/>
+      <c r="E76" s="30">
+        <v>2</v>
+      </c>
+      <c r="F76" s="30">
         <v>1</v>
       </c>
-      <c r="G76" s="24" t="s">
+      <c r="G76" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="H76" s="31" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="4">
+    <row r="77" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="21">
         <v>76</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="D77" s="6"/>
-      <c r="E77" s="2">
-        <v>2</v>
-      </c>
-      <c r="F77" s="7">
-        <v>2</v>
+      <c r="D77" s="23"/>
+      <c r="E77" s="30">
+        <v>2</v>
+      </c>
+      <c r="F77" s="32">
+        <v>2</v>
+      </c>
+      <c r="G77" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="H77" s="30" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="28">
+      <c r="A78" s="21">
         <v>77</v>
       </c>
-      <c r="B78" s="33" t="s">
+      <c r="B78" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="C78" s="33" t="s">
+      <c r="C78" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="D78" s="30"/>
-      <c r="E78" s="2">
-        <v>2</v>
-      </c>
-      <c r="F78" s="2">
+      <c r="D78" s="23"/>
+      <c r="E78" s="30">
+        <v>2</v>
+      </c>
+      <c r="F78" s="30">
         <v>1</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="G78" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="H78" s="31" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="28">
+      <c r="A79" s="21">
         <v>78</v>
       </c>
-      <c r="B79" s="33" t="s">
+      <c r="B79" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="33" t="s">
+      <c r="C79" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="D79" s="30"/>
-      <c r="E79" s="2">
-        <v>2</v>
-      </c>
-      <c r="F79" s="2">
+      <c r="D79" s="23"/>
+      <c r="E79" s="30">
+        <v>2</v>
+      </c>
+      <c r="F79" s="30">
         <v>1</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="G79" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="H79" s="31" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="4">
+    <row r="80" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="21">
         <v>79</v>
       </c>
-      <c r="B80" s="5" t="s">
+      <c r="B80" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="D80" s="6" t="s">
+      <c r="D80" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="E80" s="2">
-        <v>2</v>
-      </c>
-      <c r="F80" s="7">
-        <v>2</v>
+      <c r="E80" s="30">
+        <v>2</v>
+      </c>
+      <c r="F80" s="32">
+        <v>2</v>
+      </c>
+      <c r="G80" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H80" s="30" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="28">
+      <c r="A81" s="21">
         <v>80</v>
       </c>
-      <c r="B81" s="33" t="s">
+      <c r="B81" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="C81" s="33" t="s">
+      <c r="C81" s="26" t="s">
         <v>129</v>
       </c>
-      <c r="D81" s="30"/>
-      <c r="E81" s="2">
+      <c r="D81" s="23"/>
+      <c r="E81" s="30">
         <v>2.5</v>
       </c>
-      <c r="F81" s="2">
+      <c r="F81" s="30">
         <v>1</v>
       </c>
-      <c r="G81" s="3" t="s">
+      <c r="G81" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="H81" s="31" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="4">
+    <row r="82" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="21">
         <v>81</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="26" t="s">
         <v>130</v>
       </c>
-      <c r="D82" s="6"/>
-      <c r="E82" s="2">
+      <c r="D82" s="23"/>
+      <c r="E82" s="30">
         <v>4</v>
       </c>
-      <c r="F82" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="4">
+      <c r="F82" s="32">
+        <v>2</v>
+      </c>
+      <c r="G82" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="H82" s="30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="21">
         <v>82</v>
       </c>
-      <c r="B83" s="5" t="s">
+      <c r="B83" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="26" t="s">
         <v>131</v>
       </c>
-      <c r="D83" s="6"/>
-      <c r="E83" s="2">
-        <v>2</v>
-      </c>
-      <c r="F83" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="4">
+      <c r="D83" s="23"/>
+      <c r="E83" s="30">
+        <v>2</v>
+      </c>
+      <c r="F83" s="32">
+        <v>2</v>
+      </c>
+      <c r="G83" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H83" s="30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="21">
         <v>83</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="D84" s="6"/>
-      <c r="E84" s="2">
+      <c r="D84" s="23"/>
+      <c r="E84" s="30">
         <v>4</v>
       </c>
-      <c r="F84" s="7">
-        <v>2</v>
+      <c r="F84" s="32">
+        <v>2</v>
+      </c>
+      <c r="G84" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="H84" s="30" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="28">
+      <c r="A85" s="21">
         <v>84</v>
       </c>
-      <c r="B85" s="33" t="s">
+      <c r="B85" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C85" s="33" t="s">
+      <c r="C85" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="D85" s="30"/>
-      <c r="E85" s="2">
-        <v>2</v>
-      </c>
-      <c r="F85" s="2">
+      <c r="D85" s="23"/>
+      <c r="E85" s="30">
+        <v>2</v>
+      </c>
+      <c r="F85" s="30">
         <v>1</v>
       </c>
-      <c r="G85" s="3" t="s">
+      <c r="G85" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="H85" s="31" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="4">
+    <row r="86" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="21">
         <v>85</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="D86" s="6"/>
-      <c r="E86" s="2">
-        <v>2</v>
-      </c>
-      <c r="F86" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="4">
+      <c r="D86" s="23"/>
+      <c r="E86" s="30">
+        <v>2</v>
+      </c>
+      <c r="F86" s="32">
+        <v>2</v>
+      </c>
+      <c r="G86" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H86" s="30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="21">
         <v>86</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="D87" s="6" t="s">
+      <c r="D87" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="E87" s="2">
-        <v>2</v>
-      </c>
-      <c r="F87" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4">
+      <c r="E87" s="30">
+        <v>2</v>
+      </c>
+      <c r="F87" s="32">
+        <v>2</v>
+      </c>
+      <c r="G87" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H87" s="30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="21">
         <v>87</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="D88" s="6"/>
-      <c r="E88" s="2">
+      <c r="D88" s="23"/>
+      <c r="E88" s="30">
         <v>4</v>
       </c>
-      <c r="F88" s="7">
-        <v>2</v>
+      <c r="F88" s="32">
+        <v>2</v>
+      </c>
+      <c r="G88" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="H88" s="30" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="89" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="25"/>
-      <c r="B89" s="33"/>
-      <c r="C89" s="33"/>
-      <c r="D89" s="30"/>
+      <c r="A89" s="36"/>
+      <c r="B89" s="37"/>
+      <c r="C89" s="37"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="39"/>
     </row>
     <row r="90" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="25"/>
-      <c r="B90" s="33"/>
-      <c r="C90" s="33"/>
-      <c r="D90" s="30"/>
+      <c r="A90" s="36"/>
+      <c r="B90" s="37"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="39"/>
     </row>
     <row r="91" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="25"/>
-      <c r="B91" s="33"/>
-      <c r="C91" s="33"/>
-      <c r="D91" s="30"/>
+      <c r="A91" s="36"/>
+      <c r="B91" s="37"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="39"/>
     </row>
     <row r="92" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="6"/>
+      <c r="A92" s="36"/>
+      <c r="B92" s="37"/>
+      <c r="C92" s="37"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="39"/>
     </row>
     <row r="93" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="6"/>
+      <c r="A93" s="36"/>
+      <c r="B93" s="37"/>
+      <c r="C93" s="37"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="39"/>
     </row>
     <row r="94" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="1"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="6"/>
+      <c r="A94" s="36"/>
+      <c r="B94" s="37"/>
+      <c r="C94" s="37"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="39"/>
     </row>
     <row r="95" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="1"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="6"/>
+      <c r="A95" s="36"/>
+      <c r="B95" s="37"/>
+      <c r="C95" s="37"/>
+      <c r="D95" s="38"/>
     </row>
     <row r="96" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="1"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="6"/>
+      <c r="A96" s="36"/>
+      <c r="B96" s="37"/>
+      <c r="C96" s="37"/>
+      <c r="D96" s="38"/>
     </row>
     <row r="97" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="6"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="3"/>
     </row>
     <row r="98" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="6"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="3"/>
     </row>
     <row r="99" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="6"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="3"/>
     </row>
     <row r="100" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="6"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="3"/>
     </row>
     <row r="101" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="6"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="3"/>
     </row>
     <row r="102" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="6"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="3"/>
     </row>
     <row r="103" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="6"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="3"/>
     </row>
     <row r="104" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="6"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="3"/>
     </row>
     <row r="105" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="5"/>
-      <c r="D105" s="6"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="3"/>
     </row>
     <row r="106" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="6"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="3"/>
     </row>
     <row r="107" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="6"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="3"/>
     </row>
     <row r="108" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="6"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="3"/>
     </row>
     <row r="109" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="6"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="3"/>
     </row>
     <row r="110" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="5"/>
-      <c r="D110" s="6"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="3"/>
     </row>
     <row r="111" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="6"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="3"/>
     </row>
     <row r="112" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="6"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="3"/>
     </row>
     <row r="113" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
-      <c r="D113" s="6"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="3"/>
     </row>
     <row r="114" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="6"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="3"/>
     </row>
     <row r="115" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="6"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="3"/>
     </row>
     <row r="116" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="6"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="3"/>
     </row>
     <row r="117" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="6"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="3"/>
     </row>
     <row r="118" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5"/>
-      <c r="D118" s="6"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="3"/>
     </row>
     <row r="119" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="6"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="3"/>
     </row>
     <row r="120" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="6"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="3"/>
     </row>
     <row r="121" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="6"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="3"/>
     </row>
     <row r="122" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="6"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="3"/>
     </row>
     <row r="123" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="6"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="3"/>
     </row>
     <row r="124" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
-      <c r="D124" s="6"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="3"/>
     </row>
     <row r="125" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="5"/>
-      <c r="D125" s="6"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="3"/>
     </row>
     <row r="126" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="6"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="3"/>
     </row>
     <row r="127" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="6"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="3"/>
     </row>
     <row r="128" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="5"/>
-      <c r="D128" s="6"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="3"/>
     </row>
     <row r="129" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="6"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="3"/>
     </row>
     <row r="130" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="5"/>
-      <c r="D130" s="6"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="3"/>
     </row>
     <row r="131" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="5"/>
-      <c r="D131" s="6"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="3"/>
     </row>
     <row r="132" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="5"/>
-      <c r="D132" s="6"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="3"/>
     </row>
     <row r="133" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="5"/>
-      <c r="D133" s="6"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="3"/>
     </row>
     <row r="134" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="5"/>
-      <c r="D134" s="6"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="3"/>
     </row>
     <row r="135" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1"/>
-      <c r="B135" s="5"/>
-      <c r="C135" s="5"/>
-      <c r="D135" s="6"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="3"/>
     </row>
     <row r="136" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="5"/>
-      <c r="D136" s="6"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="3"/>
     </row>
     <row r="137" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1"/>
-      <c r="B137" s="5"/>
-      <c r="C137" s="5"/>
-      <c r="D137" s="6"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="3"/>
     </row>
     <row r="138" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="5"/>
-      <c r="D138" s="6"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="3"/>
     </row>
     <row r="139" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="5"/>
-      <c r="D139" s="6"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="3"/>
     </row>
     <row r="140" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="5"/>
-      <c r="D140" s="6"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="3"/>
     </row>
     <row r="141" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1"/>
-      <c r="B141" s="5"/>
-      <c r="C141" s="5"/>
-      <c r="D141" s="6"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="3"/>
     </row>
     <row r="142" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="5"/>
-      <c r="D142" s="6"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="3"/>
     </row>
     <row r="143" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="5"/>
-      <c r="D143" s="6"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="3"/>
     </row>
     <row r="144" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="5"/>
-      <c r="D144" s="6"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="3"/>
     </row>
     <row r="145" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="5"/>
-      <c r="D145" s="6"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="3"/>
     </row>
     <row r="146" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="5"/>
-      <c r="D146" s="6"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="3"/>
     </row>
     <row r="147" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="5"/>
-      <c r="D147" s="6"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="3"/>
     </row>
     <row r="148" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="5"/>
-      <c r="D148" s="6"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="3"/>
     </row>
     <row r="149" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="5"/>
-      <c r="D149" s="6"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="3"/>
     </row>
     <row r="150" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="5"/>
-      <c r="D150" s="6"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="3"/>
     </row>
     <row r="151" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="5"/>
-      <c r="D151" s="6"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="3"/>
     </row>
     <row r="152" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="5"/>
-      <c r="D152" s="6"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="3"/>
     </row>
     <row r="153" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="5"/>
-      <c r="D153" s="6"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="3"/>
     </row>
     <row r="154" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="5"/>
-      <c r="D154" s="6"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="3"/>
     </row>
     <row r="155" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="5"/>
-      <c r="D155" s="6"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="3"/>
     </row>
     <row r="156" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="5"/>
-      <c r="D156" s="6"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="3"/>
     </row>
     <row r="157" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="5"/>
-      <c r="D157" s="6"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="3"/>
     </row>
     <row r="158" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1"/>
-      <c r="B158" s="5"/>
-      <c r="C158" s="5"/>
-      <c r="D158" s="6"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="3"/>
     </row>
     <row r="159" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="5"/>
-      <c r="D159" s="6"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="3"/>
     </row>
     <row r="160" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="5"/>
-      <c r="D160" s="6"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="3"/>
     </row>
     <row r="161" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="5"/>
-      <c r="D161" s="6"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="3"/>
     </row>
     <row r="162" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="5"/>
-      <c r="D162" s="6"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="3"/>
     </row>
     <row r="163" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="5"/>
-      <c r="D163" s="6"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="3"/>
     </row>
     <row r="164" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="5"/>
-      <c r="D164" s="6"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="3"/>
     </row>
     <row r="165" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="5"/>
-      <c r="D165" s="6"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="3"/>
     </row>
     <row r="166" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="5"/>
-      <c r="D166" s="6"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="3"/>
     </row>
     <row r="167" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="5"/>
-      <c r="D167" s="6"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="3"/>
     </row>
     <row r="168" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="5"/>
-      <c r="D168" s="6"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="3"/>
     </row>
     <row r="169" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="5"/>
-      <c r="D169" s="6"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="3"/>
     </row>
     <row r="170" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1"/>
-      <c r="B170" s="5"/>
-      <c r="C170" s="5"/>
-      <c r="D170" s="6"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="3"/>
     </row>
     <row r="171" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="5"/>
-      <c r="D171" s="6"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="3"/>
     </row>
     <row r="172" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="5"/>
-      <c r="D172" s="6"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="3"/>
     </row>
     <row r="173" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1"/>
-      <c r="B173" s="5"/>
-      <c r="C173" s="5"/>
-      <c r="D173" s="6"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="3"/>
     </row>
     <row r="174" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1"/>
-      <c r="B174" s="5"/>
-      <c r="C174" s="5"/>
-      <c r="D174" s="6"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="3"/>
     </row>
     <row r="175" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="5"/>
-      <c r="D175" s="6"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="3"/>
     </row>
     <row r="176" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="5"/>
-      <c r="D176" s="6"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="3"/>
     </row>
     <row r="177" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="5"/>
-      <c r="D177" s="6"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="3"/>
     </row>
     <row r="178" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="5"/>
-      <c r="D178" s="6"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="3"/>
     </row>
     <row r="179" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="5"/>
-      <c r="D179" s="6"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="3"/>
     </row>
     <row r="180" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="5"/>
-      <c r="D180" s="6"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="3"/>
     </row>
     <row r="181" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1"/>
-      <c r="B181" s="5"/>
-      <c r="C181" s="5"/>
-      <c r="D181" s="6"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="3"/>
     </row>
     <row r="182" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1"/>
-      <c r="B182" s="5"/>
-      <c r="C182" s="5"/>
-      <c r="D182" s="6"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="3"/>
     </row>
     <row r="183" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="5"/>
-      <c r="D183" s="6"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="3"/>
     </row>
     <row r="184" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="5"/>
-      <c r="D184" s="6"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="3"/>
     </row>
     <row r="185" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1"/>
-      <c r="B185" s="5"/>
-      <c r="C185" s="5"/>
-      <c r="D185" s="6"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="3"/>
     </row>
     <row r="186" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1"/>
-      <c r="B186" s="5"/>
-      <c r="C186" s="5"/>
-      <c r="D186" s="6"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="3"/>
     </row>
     <row r="187" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="5"/>
-      <c r="D187" s="6"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="3"/>
     </row>
     <row r="188" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="5"/>
-      <c r="D188" s="6"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="3"/>
     </row>
     <row r="189" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1"/>
-      <c r="B189" s="5"/>
-      <c r="C189" s="5"/>
-      <c r="D189" s="6"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="3"/>
     </row>
     <row r="190" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1"/>
-      <c r="B190" s="5"/>
-      <c r="C190" s="5"/>
-      <c r="D190" s="6"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="3"/>
     </row>
     <row r="191" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1"/>
-      <c r="B191" s="5"/>
-      <c r="C191" s="5"/>
-      <c r="D191" s="6"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="3"/>
     </row>
     <row r="192" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1"/>
-      <c r="B192" s="5"/>
-      <c r="C192" s="5"/>
-      <c r="D192" s="6"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="3"/>
     </row>
     <row r="193" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1"/>
-      <c r="B193" s="5"/>
-      <c r="C193" s="5"/>
-      <c r="D193" s="6"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="3"/>
     </row>
     <row r="194" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="1"/>
-      <c r="B194" s="5"/>
-      <c r="C194" s="5"/>
-      <c r="D194" s="6"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="3"/>
     </row>
     <row r="195" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="1"/>
-      <c r="B195" s="5"/>
-      <c r="C195" s="5"/>
-      <c r="D195" s="6"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="3"/>
     </row>
     <row r="196" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1"/>
-      <c r="B196" s="5"/>
-      <c r="C196" s="5"/>
-      <c r="D196" s="6"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="3"/>
     </row>
     <row r="197" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="1"/>
-      <c r="B197" s="5"/>
-      <c r="C197" s="5"/>
-      <c r="D197" s="6"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="3"/>
     </row>
     <row r="198" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="1"/>
-      <c r="B198" s="5"/>
-      <c r="C198" s="5"/>
-      <c r="D198" s="6"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="3"/>
     </row>
     <row r="199" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="1"/>
-      <c r="B199" s="5"/>
-      <c r="C199" s="5"/>
-      <c r="D199" s="6"/>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="3"/>
     </row>
     <row r="200" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="1"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="5"/>
-      <c r="D200" s="6"/>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="3"/>
     </row>
     <row r="201" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="1"/>
-      <c r="B201" s="5"/>
-      <c r="C201" s="5"/>
-      <c r="D201" s="6"/>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="3"/>
     </row>
     <row r="202" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1"/>
-      <c r="B202" s="5"/>
-      <c r="C202" s="5"/>
-      <c r="D202" s="6"/>
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="3"/>
     </row>
     <row r="203" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1"/>
-      <c r="B203" s="5"/>
-      <c r="C203" s="5"/>
-      <c r="D203" s="6"/>
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="3"/>
     </row>
     <row r="204" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="1"/>
-      <c r="B204" s="5"/>
-      <c r="C204" s="5"/>
-      <c r="D204" s="6"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="3"/>
     </row>
     <row r="205" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="1"/>
-      <c r="B205" s="5"/>
-      <c r="C205" s="5"/>
-      <c r="D205" s="6"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="3"/>
     </row>
     <row r="206" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="1"/>
-      <c r="B206" s="5"/>
-      <c r="C206" s="5"/>
-      <c r="D206" s="6"/>
+      <c r="B206" s="2"/>
+      <c r="C206" s="2"/>
+      <c r="D206" s="3"/>
     </row>
     <row r="207" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="1"/>
-      <c r="B207" s="5"/>
-      <c r="C207" s="5"/>
-      <c r="D207" s="6"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="3"/>
     </row>
     <row r="208" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="1"/>
-      <c r="B208" s="5"/>
-      <c r="C208" s="5"/>
-      <c r="D208" s="6"/>
+      <c r="B208" s="2"/>
+      <c r="C208" s="2"/>
+      <c r="D208" s="3"/>
     </row>
     <row r="209" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="1"/>
-      <c r="B209" s="5"/>
-      <c r="C209" s="5"/>
-      <c r="D209" s="6"/>
+      <c r="B209" s="2"/>
+      <c r="C209" s="2"/>
+      <c r="D209" s="3"/>
     </row>
     <row r="210" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1"/>
-      <c r="B210" s="5"/>
-      <c r="C210" s="5"/>
-      <c r="D210" s="6"/>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="3"/>
     </row>
     <row r="211" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="1"/>
-      <c r="B211" s="5"/>
-      <c r="C211" s="5"/>
-      <c r="D211" s="6"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="3"/>
     </row>
     <row r="212" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="1"/>
-      <c r="B212" s="5"/>
-      <c r="C212" s="5"/>
-      <c r="D212" s="6"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="3"/>
     </row>
     <row r="213" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="5"/>
-      <c r="D213" s="6"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="3"/>
     </row>
     <row r="214" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="1"/>
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
-      <c r="D214" s="6"/>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="3"/>
     </row>
     <row r="215" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="1"/>
-      <c r="B215" s="5"/>
-      <c r="C215" s="5"/>
-      <c r="D215" s="6"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="3"/>
     </row>
     <row r="216" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1"/>
-      <c r="B216" s="5"/>
-      <c r="C216" s="5"/>
-      <c r="D216" s="6"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="3"/>
     </row>
     <row r="217" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="1"/>
-      <c r="B217" s="5"/>
-      <c r="C217" s="5"/>
-      <c r="D217" s="6"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="3"/>
     </row>
     <row r="218" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="1"/>
-      <c r="B218" s="5"/>
-      <c r="C218" s="5"/>
-      <c r="D218" s="6"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="3"/>
     </row>
     <row r="219" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="1"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="6"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="3"/>
     </row>
     <row r="220" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="1"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="5"/>
-      <c r="D220" s="6"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="3"/>
     </row>
     <row r="221" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="1"/>
-      <c r="B221" s="5"/>
-      <c r="C221" s="5"/>
-      <c r="D221" s="6"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="3"/>
     </row>
     <row r="222" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="1"/>
-      <c r="B222" s="5"/>
-      <c r="C222" s="5"/>
-      <c r="D222" s="6"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="3"/>
     </row>
     <row r="223" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1"/>
-      <c r="B223" s="5"/>
-      <c r="C223" s="5"/>
-      <c r="D223" s="6"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="3"/>
     </row>
     <row r="224" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="1"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="5"/>
-      <c r="D224" s="6"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="3"/>
     </row>
     <row r="225" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="1"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="5"/>
-      <c r="D225" s="6"/>
+      <c r="B225" s="2"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="3"/>
     </row>
     <row r="226" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="1"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="5"/>
-      <c r="D226" s="6"/>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="3"/>
     </row>
     <row r="227" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="1"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="5"/>
-      <c r="D227" s="6"/>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="3"/>
     </row>
     <row r="228" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="1"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="5"/>
-      <c r="D228" s="6"/>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="3"/>
     </row>
     <row r="229" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="1"/>
-      <c r="B229" s="5"/>
-      <c r="C229" s="5"/>
-      <c r="D229" s="6"/>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="3"/>
     </row>
     <row r="230" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="1"/>
-      <c r="B230" s="5"/>
-      <c r="C230" s="5"/>
-      <c r="D230" s="6"/>
+      <c r="B230" s="2"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="3"/>
     </row>
     <row r="231" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="1"/>
-      <c r="B231" s="5"/>
-      <c r="C231" s="5"/>
-      <c r="D231" s="6"/>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="3"/>
     </row>
     <row r="232" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="1"/>
-      <c r="B232" s="5"/>
-      <c r="C232" s="5"/>
-      <c r="D232" s="6"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="3"/>
     </row>
     <row r="233" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1"/>
-      <c r="B233" s="5"/>
-      <c r="C233" s="5"/>
-      <c r="D233" s="6"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="3"/>
     </row>
     <row r="234" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="1"/>
-      <c r="B234" s="5"/>
-      <c r="C234" s="5"/>
-      <c r="D234" s="6"/>
+      <c r="B234" s="2"/>
+      <c r="C234" s="2"/>
+      <c r="D234" s="3"/>
     </row>
     <row r="235" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="1"/>
-      <c r="B235" s="5"/>
-      <c r="C235" s="5"/>
-      <c r="D235" s="6"/>
+      <c r="B235" s="2"/>
+      <c r="C235" s="2"/>
+      <c r="D235" s="3"/>
     </row>
     <row r="236" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="1"/>
-      <c r="B236" s="5"/>
-      <c r="C236" s="5"/>
-      <c r="D236" s="6"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="3"/>
     </row>
     <row r="237" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="1"/>
-      <c r="B237" s="5"/>
-      <c r="C237" s="5"/>
-      <c r="D237" s="6"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="3"/>
     </row>
     <row r="238" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="1"/>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
-      <c r="D238" s="6"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="3"/>
     </row>
     <row r="239" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="1"/>
-      <c r="B239" s="5"/>
-      <c r="C239" s="5"/>
-      <c r="D239" s="6"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="3"/>
     </row>
     <row r="240" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="1"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="5"/>
-      <c r="D240" s="6"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="3"/>
     </row>
     <row r="241" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="1"/>
-      <c r="B241" s="5"/>
-      <c r="C241" s="5"/>
-      <c r="D241" s="6"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="3"/>
     </row>
     <row r="242" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="1"/>
-      <c r="B242" s="5"/>
-      <c r="C242" s="5"/>
-      <c r="D242" s="6"/>
+      <c r="B242" s="2"/>
+      <c r="C242" s="2"/>
+      <c r="D242" s="3"/>
     </row>
     <row r="243" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="1"/>
-      <c r="B243" s="5"/>
-      <c r="C243" s="5"/>
-      <c r="D243" s="6"/>
+      <c r="B243" s="2"/>
+      <c r="C243" s="2"/>
+      <c r="D243" s="3"/>
     </row>
     <row r="244" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="1"/>
-      <c r="B244" s="5"/>
-      <c r="C244" s="5"/>
-      <c r="D244" s="6"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="3"/>
     </row>
     <row r="245" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="1"/>
-      <c r="B245" s="5"/>
-      <c r="C245" s="5"/>
-      <c r="D245" s="6"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="3"/>
     </row>
     <row r="246" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="1"/>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5"/>
-      <c r="D246" s="6"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="3"/>
     </row>
     <row r="247" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="1"/>
-      <c r="B247" s="5"/>
-      <c r="C247" s="5"/>
-      <c r="D247" s="6"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="3"/>
     </row>
     <row r="248" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="1"/>
-      <c r="B248" s="5"/>
-      <c r="C248" s="5"/>
-      <c r="D248" s="6"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="3"/>
     </row>
     <row r="249" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="1"/>
-      <c r="B249" s="5"/>
-      <c r="C249" s="5"/>
-      <c r="D249" s="6"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="3"/>
     </row>
     <row r="250" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="1"/>
-      <c r="B250" s="5"/>
-      <c r="C250" s="5"/>
-      <c r="D250" s="6"/>
+      <c r="B250" s="2"/>
+      <c r="C250" s="2"/>
+      <c r="D250" s="3"/>
     </row>
     <row r="251" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="1"/>
-      <c r="B251" s="5"/>
-      <c r="C251" s="5"/>
-      <c r="D251" s="6"/>
+      <c r="B251" s="2"/>
+      <c r="C251" s="2"/>
+      <c r="D251" s="3"/>
     </row>
     <row r="252" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1"/>
-      <c r="B252" s="5"/>
-      <c r="C252" s="5"/>
-      <c r="D252" s="6"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="3"/>
     </row>
     <row r="253" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1"/>
-      <c r="B253" s="5"/>
-      <c r="C253" s="5"/>
-      <c r="D253" s="6"/>
+      <c r="B253" s="2"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="3"/>
     </row>
     <row r="254" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1"/>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
-      <c r="D254" s="6"/>
+      <c r="B254" s="2"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="3"/>
     </row>
     <row r="255" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1"/>
-      <c r="B255" s="5"/>
-      <c r="C255" s="5"/>
-      <c r="D255" s="6"/>
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="3"/>
     </row>
     <row r="256" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1"/>
-      <c r="B256" s="5"/>
-      <c r="C256" s="5"/>
-      <c r="D256" s="6"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="3"/>
     </row>
     <row r="257" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1"/>
-      <c r="B257" s="5"/>
-      <c r="C257" s="5"/>
-      <c r="D257" s="6"/>
+      <c r="B257" s="2"/>
+      <c r="C257" s="2"/>
+      <c r="D257" s="3"/>
     </row>
     <row r="258" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1"/>
-      <c r="B258" s="5"/>
-      <c r="C258" s="5"/>
-      <c r="D258" s="6"/>
+      <c r="B258" s="2"/>
+      <c r="C258" s="2"/>
+      <c r="D258" s="3"/>
     </row>
     <row r="259" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1"/>
-      <c r="B259" s="5"/>
-      <c r="C259" s="5"/>
-      <c r="D259" s="6"/>
+      <c r="B259" s="2"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="3"/>
     </row>
     <row r="260" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1"/>
-      <c r="B260" s="5"/>
-      <c r="C260" s="5"/>
-      <c r="D260" s="6"/>
+      <c r="B260" s="2"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="3"/>
     </row>
     <row r="261" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1"/>
-      <c r="B261" s="5"/>
-      <c r="C261" s="5"/>
-      <c r="D261" s="6"/>
+      <c r="B261" s="2"/>
+      <c r="C261" s="2"/>
+      <c r="D261" s="3"/>
     </row>
     <row r="262" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1"/>
-      <c r="B262" s="5"/>
-      <c r="C262" s="5"/>
-      <c r="D262" s="6"/>
+      <c r="B262" s="2"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="3"/>
     </row>
     <row r="263" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1"/>
-      <c r="B263" s="5"/>
-      <c r="C263" s="5"/>
-      <c r="D263" s="6"/>
+      <c r="B263" s="2"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="3"/>
     </row>
     <row r="264" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1"/>
-      <c r="B264" s="5"/>
-      <c r="C264" s="5"/>
-      <c r="D264" s="6"/>
+      <c r="B264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="3"/>
     </row>
     <row r="265" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1"/>
-      <c r="B265" s="5"/>
-      <c r="C265" s="5"/>
-      <c r="D265" s="6"/>
+      <c r="B265" s="2"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="3"/>
     </row>
     <row r="266" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="1"/>
-      <c r="B266" s="5"/>
-      <c r="C266" s="5"/>
-      <c r="D266" s="6"/>
+      <c r="B266" s="2"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="3"/>
     </row>
     <row r="267" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="1"/>
-      <c r="B267" s="5"/>
-      <c r="C267" s="5"/>
-      <c r="D267" s="6"/>
+      <c r="B267" s="2"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="3"/>
     </row>
     <row r="268" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="1"/>
-      <c r="B268" s="5"/>
-      <c r="C268" s="5"/>
-      <c r="D268" s="6"/>
+      <c r="B268" s="2"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="3"/>
     </row>
     <row r="269" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1"/>
-      <c r="B269" s="5"/>
-      <c r="C269" s="5"/>
-      <c r="D269" s="6"/>
+      <c r="B269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="3"/>
     </row>
     <row r="270" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1"/>
-      <c r="B270" s="5"/>
-      <c r="C270" s="5"/>
-      <c r="D270" s="6"/>
+      <c r="B270" s="2"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="3"/>
     </row>
     <row r="271" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1"/>
-      <c r="B271" s="5"/>
-      <c r="C271" s="5"/>
-      <c r="D271" s="6"/>
+      <c r="B271" s="2"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="3"/>
     </row>
     <row r="272" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1"/>
-      <c r="B272" s="5"/>
-      <c r="C272" s="5"/>
-      <c r="D272" s="6"/>
+      <c r="B272" s="2"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="3"/>
     </row>
     <row r="273" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="1"/>
-      <c r="B273" s="5"/>
-      <c r="C273" s="5"/>
-      <c r="D273" s="6"/>
+      <c r="B273" s="2"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="3"/>
     </row>
     <row r="274" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="1"/>
-      <c r="B274" s="5"/>
-      <c r="C274" s="5"/>
-      <c r="D274" s="6"/>
+      <c r="B274" s="2"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="3"/>
     </row>
     <row r="275" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="1"/>
-      <c r="B275" s="5"/>
-      <c r="C275" s="5"/>
-      <c r="D275" s="6"/>
+      <c r="B275" s="2"/>
+      <c r="C275" s="2"/>
+      <c r="D275" s="3"/>
     </row>
     <row r="276" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="1"/>
-      <c r="B276" s="5"/>
-      <c r="C276" s="5"/>
-      <c r="D276" s="6"/>
+      <c r="B276" s="2"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="3"/>
     </row>
     <row r="277" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="1"/>
-      <c r="B277" s="5"/>
-      <c r="C277" s="5"/>
-      <c r="D277" s="6"/>
+      <c r="B277" s="2"/>
+      <c r="C277" s="2"/>
+      <c r="D277" s="3"/>
     </row>
     <row r="278" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="1"/>
-      <c r="B278" s="5"/>
-      <c r="C278" s="5"/>
-      <c r="D278" s="6"/>
+      <c r="B278" s="2"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="3"/>
     </row>
     <row r="279" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1"/>
-      <c r="B279" s="5"/>
-      <c r="C279" s="5"/>
-      <c r="D279" s="6"/>
+      <c r="B279" s="2"/>
+      <c r="C279" s="2"/>
+      <c r="D279" s="3"/>
     </row>
     <row r="280" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="1"/>
-      <c r="B280" s="5"/>
-      <c r="C280" s="5"/>
-      <c r="D280" s="6"/>
+      <c r="B280" s="2"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="3"/>
     </row>
     <row r="281" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="1"/>
-      <c r="B281" s="5"/>
-      <c r="C281" s="5"/>
-      <c r="D281" s="6"/>
+      <c r="B281" s="2"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="3"/>
     </row>
     <row r="282" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="1"/>
-      <c r="B282" s="5"/>
-      <c r="C282" s="5"/>
-      <c r="D282" s="6"/>
+      <c r="B282" s="2"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="3"/>
     </row>
     <row r="283" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="1"/>
-      <c r="B283" s="5"/>
-      <c r="C283" s="5"/>
-      <c r="D283" s="6"/>
+      <c r="B283" s="2"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="3"/>
     </row>
     <row r="284" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="1"/>
-      <c r="B284" s="5"/>
-      <c r="C284" s="5"/>
-      <c r="D284" s="6"/>
+      <c r="B284" s="2"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="3"/>
     </row>
     <row r="285" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="1"/>
-      <c r="B285" s="5"/>
-      <c r="C285" s="5"/>
-      <c r="D285" s="6"/>
+      <c r="B285" s="2"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="3"/>
     </row>
     <row r="286" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="1"/>
-      <c r="B286" s="5"/>
-      <c r="C286" s="5"/>
-      <c r="D286" s="6"/>
+      <c r="B286" s="2"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="3"/>
     </row>
     <row r="287" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1"/>
-      <c r="B287" s="5"/>
-      <c r="C287" s="5"/>
-      <c r="D287" s="6"/>
+      <c r="B287" s="2"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="3"/>
     </row>
     <row r="288" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="1"/>
-      <c r="B288" s="5"/>
-      <c r="C288" s="5"/>
-      <c r="D288" s="6"/>
+      <c r="B288" s="2"/>
+      <c r="C288" s="2"/>
+      <c r="D288" s="3"/>
     </row>
     <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5324,13 +5615,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A1:Y88" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Y88" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
@@ -5353,1916 +5638,1916 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.2" x14ac:dyDescent="0.35">
-      <c r="A1" s="10"/>
-      <c r="B1" s="22" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="11"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="13" t="s">
+      <c r="A2" s="8"/>
+      <c r="B2" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F2" s="12"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="11">
         <v>3</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="11">
         <v>20</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="F3" s="11"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="14">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="10">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="11">
         <v>3</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="11">
         <v>5</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="11">
         <v>3</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="11">
         <v>5</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="F5" s="11"/>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>4</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="11">
         <v>3</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="11">
         <v>5</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>5</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="11">
         <v>3</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="11">
         <v>5</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>6</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="11">
         <v>3</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="11">
         <v>5</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>7</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="11">
         <v>3</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="11">
         <v>10</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>8</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="11">
         <v>3</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="11">
         <v>5</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" ht="19.2" x14ac:dyDescent="0.35">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="18">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="14">
         <v>60</v>
       </c>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
     </row>
     <row r="12" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A13" s="12"/>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="F13" s="12"/>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="14">
+      <c r="A14" s="10">
         <v>1</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="11">
         <v>3</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="11">
         <v>10</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
-        <v>2</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="A15" s="10">
+        <v>2</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="11">
         <v>3</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="11">
         <v>10</v>
       </c>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" ht="19.2" x14ac:dyDescent="0.35">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="18">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="14">
         <v>20</v>
       </c>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
     </row>
     <row r="17" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
     </row>
     <row r="18" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
     </row>
     <row r="19" spans="1:6" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" ht="31.8" x14ac:dyDescent="0.35">
-      <c r="A20" s="11"/>
-      <c r="B20" s="17" t="s">
+      <c r="A20" s="7"/>
+      <c r="B20" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="15">
         <v>3</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="14">
         <v>20</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="F20" s="11"/>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11"/>
-      <c r="B24" s="21" t="s">
+      <c r="A24" s="7"/>
+      <c r="B24" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="18">
+      <c r="C24" s="17"/>
+      <c r="D24" s="14">
         <v>100</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
+      <c r="A34" s="7"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="11"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
+      <c r="A38" s="7"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
+      <c r="A40" s="7"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
     </row>
     <row r="41" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
     </row>
     <row r="42" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
     </row>
     <row r="43" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
     </row>
     <row r="44" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
     </row>
     <row r="45" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
+      <c r="A45" s="7"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
     </row>
     <row r="46" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
+      <c r="A46" s="7"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
     </row>
     <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
+      <c r="A47" s="7"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
     </row>
     <row r="48" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
+      <c r="A48" s="7"/>
+      <c r="B48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
     </row>
     <row r="49" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
+      <c r="A49" s="7"/>
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
     </row>
     <row r="50" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
+      <c r="A50" s="7"/>
+      <c r="B50" s="7"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="7"/>
     </row>
     <row r="51" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="11"/>
-      <c r="E51" s="11"/>
-      <c r="F51" s="11"/>
+      <c r="A51" s="7"/>
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
     </row>
     <row r="52" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="11"/>
+      <c r="A52" s="7"/>
+      <c r="B52" s="7"/>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="7"/>
     </row>
     <row r="53" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="11"/>
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
     </row>
     <row r="54" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
+      <c r="A54" s="7"/>
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
     </row>
     <row r="55" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
+      <c r="A55" s="7"/>
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="7"/>
     </row>
     <row r="56" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11"/>
+      <c r="A56" s="7"/>
+      <c r="B56" s="7"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
     </row>
     <row r="57" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
+      <c r="A57" s="7"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
     </row>
     <row r="58" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-      <c r="D58" s="11"/>
-      <c r="E58" s="11"/>
-      <c r="F58" s="11"/>
+      <c r="A58" s="7"/>
+      <c r="B58" s="7"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="7"/>
     </row>
     <row r="59" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
-      <c r="D59" s="11"/>
-      <c r="E59" s="11"/>
-      <c r="F59" s="11"/>
+      <c r="A59" s="7"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
     </row>
     <row r="60" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
+      <c r="A60" s="7"/>
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="7"/>
     </row>
     <row r="61" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="11"/>
+      <c r="A61" s="7"/>
+      <c r="B61" s="7"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
     </row>
     <row r="62" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
-      <c r="D62" s="11"/>
-      <c r="E62" s="11"/>
-      <c r="F62" s="11"/>
+      <c r="A62" s="7"/>
+      <c r="B62" s="7"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
     </row>
     <row r="63" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="11"/>
-      <c r="F63" s="11"/>
+      <c r="A63" s="7"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="7"/>
     </row>
     <row r="64" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
+      <c r="A64" s="7"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="7"/>
     </row>
     <row r="65" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
+      <c r="A65" s="7"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="7"/>
+      <c r="D65" s="7"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="7"/>
     </row>
     <row r="66" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="11"/>
+      <c r="A66" s="7"/>
+      <c r="B66" s="7"/>
+      <c r="C66" s="7"/>
+      <c r="D66" s="7"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="7"/>
     </row>
     <row r="67" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
-      <c r="C67" s="11"/>
-      <c r="D67" s="11"/>
-      <c r="E67" s="11"/>
-      <c r="F67" s="11"/>
+      <c r="A67" s="7"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
+      <c r="D67" s="7"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
     </row>
     <row r="68" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
+      <c r="A68" s="7"/>
+      <c r="B68" s="7"/>
+      <c r="C68" s="7"/>
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
     </row>
     <row r="69" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
+      <c r="A69" s="7"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
     </row>
     <row r="70" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="11"/>
+      <c r="A70" s="7"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
     </row>
     <row r="71" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
+      <c r="A71" s="7"/>
+      <c r="B71" s="7"/>
+      <c r="C71" s="7"/>
+      <c r="D71" s="7"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
     </row>
     <row r="72" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
+      <c r="A72" s="7"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
+      <c r="A73" s="7"/>
+      <c r="B73" s="7"/>
+      <c r="C73" s="7"/>
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="11"/>
+      <c r="A74" s="7"/>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7"/>
+      <c r="D74" s="7"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="7"/>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="11"/>
-      <c r="E75" s="11"/>
-      <c r="F75" s="11"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="11"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
-      <c r="D76" s="11"/>
-      <c r="E76" s="11"/>
-      <c r="F76" s="11"/>
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="7"/>
+      <c r="D76" s="7"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="7"/>
     </row>
     <row r="77" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="7"/>
+      <c r="D77" s="7"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="7"/>
     </row>
     <row r="78" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="11"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="7"/>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
     </row>
     <row r="79" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
     </row>
     <row r="80" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="11"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
     </row>
     <row r="81" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="11"/>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
     </row>
     <row r="82" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="11"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
-      <c r="D82" s="11"/>
-      <c r="E82" s="11"/>
-      <c r="F82" s="11"/>
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="7"/>
+      <c r="D82" s="7"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="7"/>
     </row>
     <row r="83" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="11"/>
-      <c r="B83" s="11"/>
-      <c r="C83" s="11"/>
-      <c r="D83" s="11"/>
-      <c r="E83" s="11"/>
-      <c r="F83" s="11"/>
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
     </row>
     <row r="84" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="11"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
     </row>
     <row r="85" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="11"/>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
+      <c r="A85" s="7"/>
+      <c r="B85" s="7"/>
+      <c r="C85" s="7"/>
+      <c r="D85" s="7"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="7"/>
     </row>
     <row r="86" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="11"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
+      <c r="A86" s="7"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="7"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="7"/>
     </row>
     <row r="87" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="11"/>
-      <c r="B87" s="11"/>
-      <c r="C87" s="11"/>
-      <c r="D87" s="11"/>
-      <c r="E87" s="11"/>
-      <c r="F87" s="11"/>
+      <c r="A87" s="7"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="7"/>
     </row>
     <row r="88" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="11"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="11"/>
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="7"/>
+      <c r="D88" s="7"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="7"/>
     </row>
     <row r="89" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="11"/>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="7"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
     </row>
     <row r="90" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="11"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
-      <c r="D90" s="11"/>
-      <c r="E90" s="11"/>
-      <c r="F90" s="11"/>
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="7"/>
+      <c r="D90" s="7"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="7"/>
     </row>
     <row r="91" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="11"/>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="7"/>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
     </row>
     <row r="92" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="11"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
     </row>
     <row r="93" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="11"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="11"/>
+      <c r="A93" s="7"/>
+      <c r="B93" s="7"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="11"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
-      <c r="D94" s="11"/>
-      <c r="E94" s="11"/>
-      <c r="F94" s="11"/>
+      <c r="A94" s="7"/>
+      <c r="B94" s="7"/>
+      <c r="C94" s="7"/>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="7"/>
     </row>
     <row r="95" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="11"/>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="11"/>
+      <c r="A95" s="7"/>
+      <c r="B95" s="7"/>
+      <c r="C95" s="7"/>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
     </row>
     <row r="96" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="11"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
-      <c r="D96" s="11"/>
-      <c r="E96" s="11"/>
-      <c r="F96" s="11"/>
+      <c r="A96" s="7"/>
+      <c r="B96" s="7"/>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
     </row>
     <row r="97" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="11"/>
-      <c r="B97" s="11"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="11"/>
+      <c r="A97" s="7"/>
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
     </row>
     <row r="98" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="11"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
+      <c r="A98" s="7"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
     </row>
     <row r="99" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="11"/>
-      <c r="B99" s="11"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="11"/>
+      <c r="A99" s="7"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="7"/>
     </row>
     <row r="100" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
-      <c r="D100" s="11"/>
-      <c r="E100" s="11"/>
-      <c r="F100" s="11"/>
+      <c r="A100" s="7"/>
+      <c r="B100" s="7"/>
+      <c r="C100" s="7"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="7"/>
     </row>
     <row r="101" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="11"/>
-      <c r="B101" s="11"/>
-      <c r="C101" s="11"/>
-      <c r="D101" s="11"/>
-      <c r="E101" s="11"/>
-      <c r="F101" s="11"/>
+      <c r="A101" s="7"/>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
     </row>
     <row r="102" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="11"/>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
+      <c r="A102" s="7"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
     </row>
     <row r="103" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="11"/>
-      <c r="B103" s="11"/>
-      <c r="C103" s="11"/>
-      <c r="D103" s="11"/>
-      <c r="E103" s="11"/>
-      <c r="F103" s="11"/>
+      <c r="A103" s="7"/>
+      <c r="B103" s="7"/>
+      <c r="C103" s="7"/>
+      <c r="D103" s="7"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="7"/>
     </row>
     <row r="104" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="11"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="11"/>
-      <c r="D104" s="11"/>
-      <c r="E104" s="11"/>
-      <c r="F104" s="11"/>
+      <c r="A104" s="7"/>
+      <c r="B104" s="7"/>
+      <c r="C104" s="7"/>
+      <c r="D104" s="7"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
     </row>
     <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="11"/>
-      <c r="B105" s="11"/>
-      <c r="C105" s="11"/>
-      <c r="D105" s="11"/>
-      <c r="E105" s="11"/>
-      <c r="F105" s="11"/>
+      <c r="A105" s="7"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="7"/>
+      <c r="D105" s="7"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="7"/>
     </row>
     <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="11"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="11"/>
-      <c r="E106" s="11"/>
-      <c r="F106" s="11"/>
+      <c r="A106" s="7"/>
+      <c r="B106" s="7"/>
+      <c r="C106" s="7"/>
+      <c r="D106" s="7"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
     </row>
     <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="11"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="11"/>
+      <c r="A107" s="7"/>
+      <c r="B107" s="7"/>
+      <c r="C107" s="7"/>
+      <c r="D107" s="7"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="7"/>
     </row>
     <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="11"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
-      <c r="F108" s="11"/>
+      <c r="A108" s="7"/>
+      <c r="B108" s="7"/>
+      <c r="C108" s="7"/>
+      <c r="D108" s="7"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="7"/>
     </row>
     <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="11"/>
-      <c r="B109" s="11"/>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
-      <c r="F109" s="11"/>
+      <c r="A109" s="7"/>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
     </row>
     <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="11"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="11"/>
+      <c r="A110" s="7"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
     </row>
     <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="11"/>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
+      <c r="A111" s="7"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="7"/>
+      <c r="D111" s="7"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="7"/>
     </row>
     <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="11"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="11"/>
+      <c r="A112" s="7"/>
+      <c r="B112" s="7"/>
+      <c r="C112" s="7"/>
+      <c r="D112" s="7"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
     </row>
     <row r="113" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="11"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
-      <c r="D113" s="11"/>
-      <c r="E113" s="11"/>
-      <c r="F113" s="11"/>
+      <c r="A113" s="7"/>
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+      <c r="E113" s="7"/>
+      <c r="F113" s="7"/>
     </row>
     <row r="114" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="11"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
-      <c r="D114" s="11"/>
-      <c r="E114" s="11"/>
-      <c r="F114" s="11"/>
+      <c r="A114" s="7"/>
+      <c r="B114" s="7"/>
+      <c r="C114" s="7"/>
+      <c r="D114" s="7"/>
+      <c r="E114" s="7"/>
+      <c r="F114" s="7"/>
     </row>
     <row r="115" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="11"/>
-      <c r="B115" s="11"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="11"/>
+      <c r="A115" s="7"/>
+      <c r="B115" s="7"/>
+      <c r="C115" s="7"/>
+      <c r="D115" s="7"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
     </row>
     <row r="116" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="11"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
+      <c r="A116" s="7"/>
+      <c r="B116" s="7"/>
+      <c r="C116" s="7"/>
+      <c r="D116" s="7"/>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7"/>
     </row>
     <row r="117" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="11"/>
-      <c r="B117" s="11"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="11"/>
+      <c r="A117" s="7"/>
+      <c r="B117" s="7"/>
+      <c r="C117" s="7"/>
+      <c r="D117" s="7"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
     </row>
     <row r="118" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="11"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="11"/>
-      <c r="D118" s="11"/>
-      <c r="E118" s="11"/>
-      <c r="F118" s="11"/>
+      <c r="A118" s="7"/>
+      <c r="B118" s="7"/>
+      <c r="C118" s="7"/>
+      <c r="D118" s="7"/>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7"/>
     </row>
     <row r="119" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="11"/>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="11"/>
+      <c r="A119" s="7"/>
+      <c r="B119" s="7"/>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
     </row>
     <row r="120" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="11"/>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="11"/>
+      <c r="A120" s="7"/>
+      <c r="B120" s="7"/>
+      <c r="C120" s="7"/>
+      <c r="D120" s="7"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
     </row>
     <row r="121" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="11"/>
-      <c r="B121" s="11"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="11"/>
+      <c r="A121" s="7"/>
+      <c r="B121" s="7"/>
+      <c r="C121" s="7"/>
+      <c r="D121" s="7"/>
+      <c r="E121" s="7"/>
+      <c r="F121" s="7"/>
     </row>
     <row r="122" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="11"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="11"/>
-      <c r="D122" s="11"/>
-      <c r="E122" s="11"/>
-      <c r="F122" s="11"/>
+      <c r="A122" s="7"/>
+      <c r="B122" s="7"/>
+      <c r="C122" s="7"/>
+      <c r="D122" s="7"/>
+      <c r="E122" s="7"/>
+      <c r="F122" s="7"/>
     </row>
     <row r="123" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="11"/>
-      <c r="B123" s="11"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="11"/>
-      <c r="E123" s="11"/>
-      <c r="F123" s="11"/>
+      <c r="A123" s="7"/>
+      <c r="B123" s="7"/>
+      <c r="C123" s="7"/>
+      <c r="D123" s="7"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
     </row>
     <row r="124" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="11"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="11"/>
+      <c r="A124" s="7"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
+      <c r="D124" s="7"/>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
     </row>
     <row r="125" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="11"/>
-      <c r="B125" s="11"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="11"/>
-      <c r="F125" s="11"/>
+      <c r="A125" s="7"/>
+      <c r="B125" s="7"/>
+      <c r="C125" s="7"/>
+      <c r="D125" s="7"/>
+      <c r="E125" s="7"/>
+      <c r="F125" s="7"/>
     </row>
     <row r="126" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="11"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="11"/>
-      <c r="F126" s="11"/>
+      <c r="A126" s="7"/>
+      <c r="B126" s="7"/>
+      <c r="C126" s="7"/>
+      <c r="D126" s="7"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
     </row>
     <row r="127" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="11"/>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
+      <c r="A127" s="7"/>
+      <c r="B127" s="7"/>
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7"/>
     </row>
     <row r="128" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="11"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="11"/>
-      <c r="F128" s="11"/>
+      <c r="A128" s="7"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
+      <c r="F128" s="7"/>
     </row>
     <row r="129" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="11"/>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="11"/>
-      <c r="F129" s="11"/>
+      <c r="A129" s="7"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
+      <c r="D129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
     </row>
     <row r="130" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="11"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="11"/>
-      <c r="F130" s="11"/>
+      <c r="A130" s="7"/>
+      <c r="B130" s="7"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
     </row>
     <row r="131" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="11"/>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="11"/>
-      <c r="F131" s="11"/>
+      <c r="A131" s="7"/>
+      <c r="B131" s="7"/>
+      <c r="C131" s="7"/>
+      <c r="D131" s="7"/>
+      <c r="E131" s="7"/>
+      <c r="F131" s="7"/>
     </row>
     <row r="132" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="11"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="11"/>
-      <c r="F132" s="11"/>
+      <c r="A132" s="7"/>
+      <c r="B132" s="7"/>
+      <c r="C132" s="7"/>
+      <c r="D132" s="7"/>
+      <c r="E132" s="7"/>
+      <c r="F132" s="7"/>
     </row>
     <row r="133" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="11"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
+      <c r="A133" s="7"/>
+      <c r="B133" s="7"/>
+      <c r="C133" s="7"/>
+      <c r="D133" s="7"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
     </row>
     <row r="134" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="11"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="11"/>
-      <c r="E134" s="11"/>
-      <c r="F134" s="11"/>
+      <c r="A134" s="7"/>
+      <c r="B134" s="7"/>
+      <c r="C134" s="7"/>
+      <c r="D134" s="7"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
     </row>
     <row r="135" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="11"/>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
-      <c r="F135" s="11"/>
+      <c r="A135" s="7"/>
+      <c r="B135" s="7"/>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
     </row>
     <row r="136" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="11"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
+      <c r="A136" s="7"/>
+      <c r="B136" s="7"/>
+      <c r="C136" s="7"/>
+      <c r="D136" s="7"/>
+      <c r="E136" s="7"/>
+      <c r="F136" s="7"/>
     </row>
     <row r="137" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="11"/>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="11"/>
-      <c r="F137" s="11"/>
+      <c r="A137" s="7"/>
+      <c r="B137" s="7"/>
+      <c r="C137" s="7"/>
+      <c r="D137" s="7"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
     </row>
     <row r="138" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="11"/>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
-      <c r="D138" s="11"/>
-      <c r="E138" s="11"/>
-      <c r="F138" s="11"/>
+      <c r="A138" s="7"/>
+      <c r="B138" s="7"/>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
     </row>
     <row r="139" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="11"/>
-      <c r="B139" s="11"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
+      <c r="A139" s="7"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="7"/>
+      <c r="D139" s="7"/>
+      <c r="E139" s="7"/>
+      <c r="F139" s="7"/>
     </row>
     <row r="140" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="11"/>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
-      <c r="F140" s="11"/>
+      <c r="A140" s="7"/>
+      <c r="B140" s="7"/>
+      <c r="C140" s="7"/>
+      <c r="D140" s="7"/>
+      <c r="E140" s="7"/>
+      <c r="F140" s="7"/>
     </row>
     <row r="141" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="11"/>
-      <c r="B141" s="11"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
-      <c r="F141" s="11"/>
+      <c r="A141" s="7"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
     </row>
     <row r="142" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="11"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
-      <c r="F142" s="11"/>
+      <c r="A142" s="7"/>
+      <c r="B142" s="7"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
     </row>
     <row r="143" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="11"/>
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
+      <c r="A143" s="7"/>
+      <c r="B143" s="7"/>
+      <c r="C143" s="7"/>
+      <c r="D143" s="7"/>
+      <c r="E143" s="7"/>
+      <c r="F143" s="7"/>
     </row>
     <row r="144" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="11"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
-      <c r="F144" s="11"/>
+      <c r="A144" s="7"/>
+      <c r="B144" s="7"/>
+      <c r="C144" s="7"/>
+      <c r="D144" s="7"/>
+      <c r="E144" s="7"/>
+      <c r="F144" s="7"/>
     </row>
     <row r="145" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="11"/>
-      <c r="B145" s="11"/>
-      <c r="C145" s="11"/>
-      <c r="D145" s="11"/>
-      <c r="E145" s="11"/>
-      <c r="F145" s="11"/>
+      <c r="A145" s="7"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
+      <c r="D145" s="7"/>
+      <c r="E145" s="7"/>
+      <c r="F145" s="7"/>
     </row>
     <row r="146" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="11"/>
-      <c r="B146" s="11"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
-      <c r="F146" s="11"/>
+      <c r="A146" s="7"/>
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
+      <c r="D146" s="7"/>
+      <c r="E146" s="7"/>
+      <c r="F146" s="7"/>
     </row>
     <row r="147" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="11"/>
-      <c r="B147" s="11"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="11"/>
-      <c r="F147" s="11"/>
+      <c r="A147" s="7"/>
+      <c r="B147" s="7"/>
+      <c r="C147" s="7"/>
+      <c r="D147" s="7"/>
+      <c r="E147" s="7"/>
+      <c r="F147" s="7"/>
     </row>
     <row r="148" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="11"/>
-      <c r="B148" s="11"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="11"/>
-      <c r="E148" s="11"/>
-      <c r="F148" s="11"/>
+      <c r="A148" s="7"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
     </row>
     <row r="149" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="11"/>
-      <c r="B149" s="11"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="11"/>
-      <c r="F149" s="11"/>
+      <c r="A149" s="7"/>
+      <c r="B149" s="7"/>
+      <c r="C149" s="7"/>
+      <c r="D149" s="7"/>
+      <c r="E149" s="7"/>
+      <c r="F149" s="7"/>
     </row>
     <row r="150" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="11"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="11"/>
-      <c r="D150" s="11"/>
-      <c r="E150" s="11"/>
-      <c r="F150" s="11"/>
+      <c r="A150" s="7"/>
+      <c r="B150" s="7"/>
+      <c r="C150" s="7"/>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="7"/>
     </row>
     <row r="151" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="11"/>
-      <c r="B151" s="11"/>
-      <c r="C151" s="11"/>
-      <c r="D151" s="11"/>
-      <c r="E151" s="11"/>
-      <c r="F151" s="11"/>
+      <c r="A151" s="7"/>
+      <c r="B151" s="7"/>
+      <c r="C151" s="7"/>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="7"/>
     </row>
     <row r="152" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="11"/>
-      <c r="B152" s="11"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
-      <c r="F152" s="11"/>
+      <c r="A152" s="7"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="7"/>
+      <c r="D152" s="7"/>
+      <c r="E152" s="7"/>
+      <c r="F152" s="7"/>
     </row>
     <row r="153" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="11"/>
-      <c r="B153" s="11"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11"/>
-      <c r="F153" s="11"/>
+      <c r="A153" s="7"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
     </row>
     <row r="154" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="11"/>
-      <c r="B154" s="11"/>
-      <c r="C154" s="11"/>
-      <c r="D154" s="11"/>
-      <c r="E154" s="11"/>
-      <c r="F154" s="11"/>
+      <c r="A154" s="7"/>
+      <c r="B154" s="7"/>
+      <c r="C154" s="7"/>
+      <c r="D154" s="7"/>
+      <c r="E154" s="7"/>
+      <c r="F154" s="7"/>
     </row>
     <row r="155" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="11"/>
-      <c r="B155" s="11"/>
-      <c r="C155" s="11"/>
-      <c r="D155" s="11"/>
-      <c r="E155" s="11"/>
-      <c r="F155" s="11"/>
+      <c r="A155" s="7"/>
+      <c r="B155" s="7"/>
+      <c r="C155" s="7"/>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+      <c r="F155" s="7"/>
     </row>
     <row r="156" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="11"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="11"/>
-      <c r="F156" s="11"/>
+      <c r="A156" s="7"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="7"/>
+      <c r="D156" s="7"/>
+      <c r="E156" s="7"/>
+      <c r="F156" s="7"/>
     </row>
     <row r="157" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="11"/>
-      <c r="B157" s="11"/>
-      <c r="C157" s="11"/>
-      <c r="D157" s="11"/>
-      <c r="E157" s="11"/>
-      <c r="F157" s="11"/>
+      <c r="A157" s="7"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7"/>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
     </row>
     <row r="158" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="11"/>
-      <c r="B158" s="11"/>
-      <c r="C158" s="11"/>
-      <c r="D158" s="11"/>
-      <c r="E158" s="11"/>
-      <c r="F158" s="11"/>
+      <c r="A158" s="7"/>
+      <c r="B158" s="7"/>
+      <c r="C158" s="7"/>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="7"/>
     </row>
     <row r="159" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="11"/>
-      <c r="B159" s="11"/>
-      <c r="C159" s="11"/>
-      <c r="D159" s="11"/>
-      <c r="E159" s="11"/>
-      <c r="F159" s="11"/>
+      <c r="A159" s="7"/>
+      <c r="B159" s="7"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
     </row>
     <row r="160" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="11"/>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="11"/>
-      <c r="F160" s="11"/>
+      <c r="A160" s="7"/>
+      <c r="B160" s="7"/>
+      <c r="C160" s="7"/>
+      <c r="D160" s="7"/>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
     </row>
     <row r="161" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="11"/>
-      <c r="B161" s="11"/>
-      <c r="C161" s="11"/>
-      <c r="D161" s="11"/>
-      <c r="E161" s="11"/>
-      <c r="F161" s="11"/>
+      <c r="A161" s="7"/>
+      <c r="B161" s="7"/>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
+      <c r="E161" s="7"/>
+      <c r="F161" s="7"/>
     </row>
     <row r="162" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="11"/>
-      <c r="B162" s="11"/>
-      <c r="C162" s="11"/>
-      <c r="D162" s="11"/>
-      <c r="E162" s="11"/>
-      <c r="F162" s="11"/>
+      <c r="A162" s="7"/>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
     </row>
     <row r="163" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="11"/>
-      <c r="B163" s="11"/>
-      <c r="C163" s="11"/>
-      <c r="D163" s="11"/>
-      <c r="E163" s="11"/>
-      <c r="F163" s="11"/>
+      <c r="A163" s="7"/>
+      <c r="B163" s="7"/>
+      <c r="C163" s="7"/>
+      <c r="D163" s="7"/>
+      <c r="E163" s="7"/>
+      <c r="F163" s="7"/>
     </row>
     <row r="164" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="11"/>
-      <c r="B164" s="11"/>
-      <c r="C164" s="11"/>
-      <c r="D164" s="11"/>
-      <c r="E164" s="11"/>
-      <c r="F164" s="11"/>
+      <c r="A164" s="7"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="7"/>
+      <c r="D164" s="7"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
     </row>
     <row r="165" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="11"/>
-      <c r="B165" s="11"/>
-      <c r="C165" s="11"/>
-      <c r="D165" s="11"/>
-      <c r="E165" s="11"/>
-      <c r="F165" s="11"/>
+      <c r="A165" s="7"/>
+      <c r="B165" s="7"/>
+      <c r="C165" s="7"/>
+      <c r="D165" s="7"/>
+      <c r="E165" s="7"/>
+      <c r="F165" s="7"/>
     </row>
     <row r="166" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="11"/>
-      <c r="B166" s="11"/>
-      <c r="C166" s="11"/>
-      <c r="D166" s="11"/>
-      <c r="E166" s="11"/>
-      <c r="F166" s="11"/>
+      <c r="A166" s="7"/>
+      <c r="B166" s="7"/>
+      <c r="C166" s="7"/>
+      <c r="D166" s="7"/>
+      <c r="E166" s="7"/>
+      <c r="F166" s="7"/>
     </row>
     <row r="167" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="11"/>
-      <c r="B167" s="11"/>
-      <c r="C167" s="11"/>
-      <c r="D167" s="11"/>
-      <c r="E167" s="11"/>
-      <c r="F167" s="11"/>
+      <c r="A167" s="7"/>
+      <c r="B167" s="7"/>
+      <c r="C167" s="7"/>
+      <c r="D167" s="7"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
     </row>
     <row r="168" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="11"/>
-      <c r="B168" s="11"/>
-      <c r="C168" s="11"/>
-      <c r="D168" s="11"/>
-      <c r="E168" s="11"/>
-      <c r="F168" s="11"/>
+      <c r="A168" s="7"/>
+      <c r="B168" s="7"/>
+      <c r="C168" s="7"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
     </row>
     <row r="169" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="11"/>
-      <c r="B169" s="11"/>
-      <c r="C169" s="11"/>
-      <c r="D169" s="11"/>
-      <c r="E169" s="11"/>
-      <c r="F169" s="11"/>
+      <c r="A169" s="7"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7"/>
+      <c r="E169" s="7"/>
+      <c r="F169" s="7"/>
     </row>
     <row r="170" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="11"/>
-      <c r="B170" s="11"/>
-      <c r="C170" s="11"/>
-      <c r="D170" s="11"/>
-      <c r="E170" s="11"/>
-      <c r="F170" s="11"/>
+      <c r="A170" s="7"/>
+      <c r="B170" s="7"/>
+      <c r="C170" s="7"/>
+      <c r="D170" s="7"/>
+      <c r="E170" s="7"/>
+      <c r="F170" s="7"/>
     </row>
     <row r="171" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="11"/>
-      <c r="B171" s="11"/>
-      <c r="C171" s="11"/>
-      <c r="D171" s="11"/>
-      <c r="E171" s="11"/>
-      <c r="F171" s="11"/>
+      <c r="A171" s="7"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
     </row>
     <row r="172" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="11"/>
-      <c r="B172" s="11"/>
-      <c r="C172" s="11"/>
-      <c r="D172" s="11"/>
-      <c r="E172" s="11"/>
-      <c r="F172" s="11"/>
+      <c r="A172" s="7"/>
+      <c r="B172" s="7"/>
+      <c r="C172" s="7"/>
+      <c r="D172" s="7"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7"/>
     </row>
     <row r="173" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="11"/>
-      <c r="B173" s="11"/>
-      <c r="C173" s="11"/>
-      <c r="D173" s="11"/>
-      <c r="E173" s="11"/>
-      <c r="F173" s="11"/>
+      <c r="A173" s="7"/>
+      <c r="B173" s="7"/>
+      <c r="C173" s="7"/>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+      <c r="F173" s="7"/>
     </row>
     <row r="174" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="11"/>
-      <c r="B174" s="11"/>
-      <c r="C174" s="11"/>
-      <c r="D174" s="11"/>
-      <c r="E174" s="11"/>
-      <c r="F174" s="11"/>
+      <c r="A174" s="7"/>
+      <c r="B174" s="7"/>
+      <c r="C174" s="7"/>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+      <c r="F174" s="7"/>
     </row>
     <row r="175" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="11"/>
-      <c r="B175" s="11"/>
-      <c r="C175" s="11"/>
-      <c r="D175" s="11"/>
-      <c r="E175" s="11"/>
-      <c r="F175" s="11"/>
+      <c r="A175" s="7"/>
+      <c r="B175" s="7"/>
+      <c r="C175" s="7"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
     </row>
     <row r="176" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="11"/>
-      <c r="B176" s="11"/>
-      <c r="C176" s="11"/>
-      <c r="D176" s="11"/>
-      <c r="E176" s="11"/>
-      <c r="F176" s="11"/>
+      <c r="A176" s="7"/>
+      <c r="B176" s="7"/>
+      <c r="C176" s="7"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
+      <c r="F176" s="7"/>
     </row>
     <row r="177" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="11"/>
-      <c r="B177" s="11"/>
-      <c r="C177" s="11"/>
-      <c r="D177" s="11"/>
-      <c r="E177" s="11"/>
-      <c r="F177" s="11"/>
+      <c r="A177" s="7"/>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
     </row>
     <row r="178" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="11"/>
-      <c r="B178" s="11"/>
-      <c r="C178" s="11"/>
-      <c r="D178" s="11"/>
-      <c r="E178" s="11"/>
-      <c r="F178" s="11"/>
+      <c r="A178" s="7"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
     </row>
     <row r="179" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="11"/>
-      <c r="B179" s="11"/>
-      <c r="C179" s="11"/>
-      <c r="D179" s="11"/>
-      <c r="E179" s="11"/>
-      <c r="F179" s="11"/>
+      <c r="A179" s="7"/>
+      <c r="B179" s="7"/>
+      <c r="C179" s="7"/>
+      <c r="D179" s="7"/>
+      <c r="E179" s="7"/>
+      <c r="F179" s="7"/>
     </row>
     <row r="180" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="11"/>
-      <c r="B180" s="11"/>
-      <c r="C180" s="11"/>
-      <c r="D180" s="11"/>
-      <c r="E180" s="11"/>
-      <c r="F180" s="11"/>
+      <c r="A180" s="7"/>
+      <c r="B180" s="7"/>
+      <c r="C180" s="7"/>
+      <c r="D180" s="7"/>
+      <c r="E180" s="7"/>
+      <c r="F180" s="7"/>
     </row>
     <row r="181" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="11"/>
-      <c r="B181" s="11"/>
-      <c r="C181" s="11"/>
-      <c r="D181" s="11"/>
-      <c r="E181" s="11"/>
-      <c r="F181" s="11"/>
+      <c r="A181" s="7"/>
+      <c r="B181" s="7"/>
+      <c r="C181" s="7"/>
+      <c r="D181" s="7"/>
+      <c r="E181" s="7"/>
+      <c r="F181" s="7"/>
     </row>
     <row r="182" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="11"/>
-      <c r="B182" s="11"/>
-      <c r="C182" s="11"/>
-      <c r="D182" s="11"/>
-      <c r="E182" s="11"/>
-      <c r="F182" s="11"/>
+      <c r="A182" s="7"/>
+      <c r="B182" s="7"/>
+      <c r="C182" s="7"/>
+      <c r="D182" s="7"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
     </row>
     <row r="183" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="11"/>
-      <c r="B183" s="11"/>
-      <c r="C183" s="11"/>
-      <c r="D183" s="11"/>
-      <c r="E183" s="11"/>
-      <c r="F183" s="11"/>
+      <c r="A183" s="7"/>
+      <c r="B183" s="7"/>
+      <c r="C183" s="7"/>
+      <c r="D183" s="7"/>
+      <c r="E183" s="7"/>
+      <c r="F183" s="7"/>
     </row>
     <row r="184" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="11"/>
-      <c r="B184" s="11"/>
-      <c r="C184" s="11"/>
-      <c r="D184" s="11"/>
-      <c r="E184" s="11"/>
-      <c r="F184" s="11"/>
+      <c r="A184" s="7"/>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
     </row>
     <row r="185" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="11"/>
-      <c r="B185" s="11"/>
-      <c r="C185" s="11"/>
-      <c r="D185" s="11"/>
-      <c r="E185" s="11"/>
-      <c r="F185" s="11"/>
+      <c r="A185" s="7"/>
+      <c r="B185" s="7"/>
+      <c r="C185" s="7"/>
+      <c r="D185" s="7"/>
+      <c r="E185" s="7"/>
+      <c r="F185" s="7"/>
     </row>
     <row r="186" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="11"/>
-      <c r="B186" s="11"/>
-      <c r="C186" s="11"/>
-      <c r="D186" s="11"/>
-      <c r="E186" s="11"/>
-      <c r="F186" s="11"/>
+      <c r="A186" s="7"/>
+      <c r="B186" s="7"/>
+      <c r="C186" s="7"/>
+      <c r="D186" s="7"/>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
     </row>
     <row r="187" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="11"/>
-      <c r="B187" s="11"/>
-      <c r="C187" s="11"/>
-      <c r="D187" s="11"/>
-      <c r="E187" s="11"/>
-      <c r="F187" s="11"/>
+      <c r="A187" s="7"/>
+      <c r="B187" s="7"/>
+      <c r="C187" s="7"/>
+      <c r="D187" s="7"/>
+      <c r="E187" s="7"/>
+      <c r="F187" s="7"/>
     </row>
     <row r="188" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="11"/>
-      <c r="B188" s="11"/>
-      <c r="C188" s="11"/>
-      <c r="D188" s="11"/>
-      <c r="E188" s="11"/>
-      <c r="F188" s="11"/>
+      <c r="A188" s="7"/>
+      <c r="B188" s="7"/>
+      <c r="C188" s="7"/>
+      <c r="D188" s="7"/>
+      <c r="E188" s="7"/>
+      <c r="F188" s="7"/>
     </row>
     <row r="189" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="11"/>
-      <c r="B189" s="11"/>
-      <c r="C189" s="11"/>
-      <c r="D189" s="11"/>
-      <c r="E189" s="11"/>
-      <c r="F189" s="11"/>
+      <c r="A189" s="7"/>
+      <c r="B189" s="7"/>
+      <c r="C189" s="7"/>
+      <c r="D189" s="7"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="7"/>
     </row>
     <row r="190" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="11"/>
-      <c r="B190" s="11"/>
-      <c r="C190" s="11"/>
-      <c r="D190" s="11"/>
-      <c r="E190" s="11"/>
-      <c r="F190" s="11"/>
+      <c r="A190" s="7"/>
+      <c r="B190" s="7"/>
+      <c r="C190" s="7"/>
+      <c r="D190" s="7"/>
+      <c r="E190" s="7"/>
+      <c r="F190" s="7"/>
     </row>
     <row r="191" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="11"/>
-      <c r="B191" s="11"/>
-      <c r="C191" s="11"/>
-      <c r="D191" s="11"/>
-      <c r="E191" s="11"/>
-      <c r="F191" s="11"/>
+      <c r="A191" s="7"/>
+      <c r="B191" s="7"/>
+      <c r="C191" s="7"/>
+      <c r="D191" s="7"/>
+      <c r="E191" s="7"/>
+      <c r="F191" s="7"/>
     </row>
     <row r="192" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="11"/>
-      <c r="B192" s="11"/>
-      <c r="C192" s="11"/>
-      <c r="D192" s="11"/>
-      <c r="E192" s="11"/>
-      <c r="F192" s="11"/>
+      <c r="A192" s="7"/>
+      <c r="B192" s="7"/>
+      <c r="C192" s="7"/>
+      <c r="D192" s="7"/>
+      <c r="E192" s="7"/>
+      <c r="F192" s="7"/>
     </row>
     <row r="193" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="11"/>
-      <c r="B193" s="11"/>
-      <c r="C193" s="11"/>
-      <c r="D193" s="11"/>
-      <c r="E193" s="11"/>
-      <c r="F193" s="11"/>
+      <c r="A193" s="7"/>
+      <c r="B193" s="7"/>
+      <c r="C193" s="7"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
     </row>
     <row r="194" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="11"/>
-      <c r="B194" s="11"/>
-      <c r="C194" s="11"/>
-      <c r="D194" s="11"/>
-      <c r="E194" s="11"/>
-      <c r="F194" s="11"/>
+      <c r="A194" s="7"/>
+      <c r="B194" s="7"/>
+      <c r="C194" s="7"/>
+      <c r="D194" s="7"/>
+      <c r="E194" s="7"/>
+      <c r="F194" s="7"/>
     </row>
     <row r="195" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="11"/>
-      <c r="B195" s="11"/>
-      <c r="C195" s="11"/>
-      <c r="D195" s="11"/>
-      <c r="E195" s="11"/>
-      <c r="F195" s="11"/>
+      <c r="A195" s="7"/>
+      <c r="B195" s="7"/>
+      <c r="C195" s="7"/>
+      <c r="D195" s="7"/>
+      <c r="E195" s="7"/>
+      <c r="F195" s="7"/>
     </row>
     <row r="196" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="11"/>
-      <c r="B196" s="11"/>
-      <c r="C196" s="11"/>
-      <c r="D196" s="11"/>
-      <c r="E196" s="11"/>
-      <c r="F196" s="11"/>
+      <c r="A196" s="7"/>
+      <c r="B196" s="7"/>
+      <c r="C196" s="7"/>
+      <c r="D196" s="7"/>
+      <c r="E196" s="7"/>
+      <c r="F196" s="7"/>
     </row>
     <row r="197" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="11"/>
-      <c r="B197" s="11"/>
-      <c r="C197" s="11"/>
-      <c r="D197" s="11"/>
-      <c r="E197" s="11"/>
-      <c r="F197" s="11"/>
+      <c r="A197" s="7"/>
+      <c r="B197" s="7"/>
+      <c r="C197" s="7"/>
+      <c r="D197" s="7"/>
+      <c r="E197" s="7"/>
+      <c r="F197" s="7"/>
     </row>
     <row r="198" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="11"/>
-      <c r="B198" s="11"/>
-      <c r="C198" s="11"/>
-      <c r="D198" s="11"/>
-      <c r="E198" s="11"/>
-      <c r="F198" s="11"/>
+      <c r="A198" s="7"/>
+      <c r="B198" s="7"/>
+      <c r="C198" s="7"/>
+      <c r="D198" s="7"/>
+      <c r="E198" s="7"/>
+      <c r="F198" s="7"/>
     </row>
     <row r="199" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="11"/>
-      <c r="B199" s="11"/>
-      <c r="C199" s="11"/>
-      <c r="D199" s="11"/>
-      <c r="E199" s="11"/>
-      <c r="F199" s="11"/>
+      <c r="A199" s="7"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="7"/>
+      <c r="D199" s="7"/>
+      <c r="E199" s="7"/>
+      <c r="F199" s="7"/>
     </row>
     <row r="200" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="11"/>
-      <c r="B200" s="11"/>
-      <c r="C200" s="11"/>
-      <c r="D200" s="11"/>
-      <c r="E200" s="11"/>
-      <c r="F200" s="11"/>
+      <c r="A200" s="7"/>
+      <c r="B200" s="7"/>
+      <c r="C200" s="7"/>
+      <c r="D200" s="7"/>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
     </row>
     <row r="201" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="11"/>
-      <c r="B201" s="11"/>
-      <c r="C201" s="11"/>
-      <c r="D201" s="11"/>
-      <c r="E201" s="11"/>
-      <c r="F201" s="11"/>
+      <c r="A201" s="7"/>
+      <c r="B201" s="7"/>
+      <c r="C201" s="7"/>
+      <c r="D201" s="7"/>
+      <c r="E201" s="7"/>
+      <c r="F201" s="7"/>
     </row>
     <row r="202" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="11"/>
-      <c r="B202" s="11"/>
-      <c r="C202" s="11"/>
-      <c r="D202" s="11"/>
-      <c r="E202" s="11"/>
-      <c r="F202" s="11"/>
+      <c r="A202" s="7"/>
+      <c r="B202" s="7"/>
+      <c r="C202" s="7"/>
+      <c r="D202" s="7"/>
+      <c r="E202" s="7"/>
+      <c r="F202" s="7"/>
     </row>
     <row r="203" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="11"/>
-      <c r="B203" s="11"/>
-      <c r="C203" s="11"/>
-      <c r="D203" s="11"/>
-      <c r="E203" s="11"/>
-      <c r="F203" s="11"/>
+      <c r="A203" s="7"/>
+      <c r="B203" s="7"/>
+      <c r="C203" s="7"/>
+      <c r="D203" s="7"/>
+      <c r="E203" s="7"/>
+      <c r="F203" s="7"/>
     </row>
     <row r="204" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="11"/>
-      <c r="B204" s="11"/>
-      <c r="C204" s="11"/>
-      <c r="D204" s="11"/>
-      <c r="E204" s="11"/>
-      <c r="F204" s="11"/>
+      <c r="A204" s="7"/>
+      <c r="B204" s="7"/>
+      <c r="C204" s="7"/>
+      <c r="D204" s="7"/>
+      <c r="E204" s="7"/>
+      <c r="F204" s="7"/>
     </row>
     <row r="205" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="11"/>
-      <c r="B205" s="11"/>
-      <c r="C205" s="11"/>
-      <c r="D205" s="11"/>
-      <c r="E205" s="11"/>
-      <c r="F205" s="11"/>
+      <c r="A205" s="7"/>
+      <c r="B205" s="7"/>
+      <c r="C205" s="7"/>
+      <c r="D205" s="7"/>
+      <c r="E205" s="7"/>
+      <c r="F205" s="7"/>
     </row>
     <row r="206" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="11"/>
-      <c r="B206" s="11"/>
-      <c r="C206" s="11"/>
-      <c r="D206" s="11"/>
-      <c r="E206" s="11"/>
-      <c r="F206" s="11"/>
+      <c r="A206" s="7"/>
+      <c r="B206" s="7"/>
+      <c r="C206" s="7"/>
+      <c r="D206" s="7"/>
+      <c r="E206" s="7"/>
+      <c r="F206" s="7"/>
     </row>
     <row r="207" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="11"/>
-      <c r="B207" s="11"/>
-      <c r="C207" s="11"/>
-      <c r="D207" s="11"/>
-      <c r="E207" s="11"/>
-      <c r="F207" s="11"/>
+      <c r="A207" s="7"/>
+      <c r="B207" s="7"/>
+      <c r="C207" s="7"/>
+      <c r="D207" s="7"/>
+      <c r="E207" s="7"/>
+      <c r="F207" s="7"/>
     </row>
     <row r="208" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="11"/>
-      <c r="B208" s="11"/>
-      <c r="C208" s="11"/>
-      <c r="D208" s="11"/>
-      <c r="E208" s="11"/>
-      <c r="F208" s="11"/>
+      <c r="A208" s="7"/>
+      <c r="B208" s="7"/>
+      <c r="C208" s="7"/>
+      <c r="D208" s="7"/>
+      <c r="E208" s="7"/>
+      <c r="F208" s="7"/>
     </row>
     <row r="209" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="11"/>
-      <c r="B209" s="11"/>
-      <c r="C209" s="11"/>
-      <c r="D209" s="11"/>
-      <c r="E209" s="11"/>
-      <c r="F209" s="11"/>
+      <c r="A209" s="7"/>
+      <c r="B209" s="7"/>
+      <c r="C209" s="7"/>
+      <c r="D209" s="7"/>
+      <c r="E209" s="7"/>
+      <c r="F209" s="7"/>
     </row>
     <row r="210" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="11"/>
-      <c r="B210" s="11"/>
-      <c r="C210" s="11"/>
-      <c r="D210" s="11"/>
-      <c r="E210" s="11"/>
-      <c r="F210" s="11"/>
+      <c r="A210" s="7"/>
+      <c r="B210" s="7"/>
+      <c r="C210" s="7"/>
+      <c r="D210" s="7"/>
+      <c r="E210" s="7"/>
+      <c r="F210" s="7"/>
     </row>
     <row r="211" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="11"/>
-      <c r="B211" s="11"/>
-      <c r="C211" s="11"/>
-      <c r="D211" s="11"/>
-      <c r="E211" s="11"/>
-      <c r="F211" s="11"/>
+      <c r="A211" s="7"/>
+      <c r="B211" s="7"/>
+      <c r="C211" s="7"/>
+      <c r="D211" s="7"/>
+      <c r="E211" s="7"/>
+      <c r="F211" s="7"/>
     </row>
     <row r="212" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="11"/>
-      <c r="B212" s="11"/>
-      <c r="C212" s="11"/>
-      <c r="D212" s="11"/>
-      <c r="E212" s="11"/>
-      <c r="F212" s="11"/>
+      <c r="A212" s="7"/>
+      <c r="B212" s="7"/>
+      <c r="C212" s="7"/>
+      <c r="D212" s="7"/>
+      <c r="E212" s="7"/>
+      <c r="F212" s="7"/>
     </row>
     <row r="213" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="11"/>
-      <c r="B213" s="11"/>
-      <c r="C213" s="11"/>
-      <c r="D213" s="11"/>
-      <c r="E213" s="11"/>
-      <c r="F213" s="11"/>
+      <c r="A213" s="7"/>
+      <c r="B213" s="7"/>
+      <c r="C213" s="7"/>
+      <c r="D213" s="7"/>
+      <c r="E213" s="7"/>
+      <c r="F213" s="7"/>
     </row>
     <row r="214" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="11"/>
-      <c r="B214" s="11"/>
-      <c r="C214" s="11"/>
-      <c r="D214" s="11"/>
-      <c r="E214" s="11"/>
-      <c r="F214" s="11"/>
+      <c r="A214" s="7"/>
+      <c r="B214" s="7"/>
+      <c r="C214" s="7"/>
+      <c r="D214" s="7"/>
+      <c r="E214" s="7"/>
+      <c r="F214" s="7"/>
     </row>
     <row r="215" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="11"/>
-      <c r="B215" s="11"/>
-      <c r="C215" s="11"/>
-      <c r="D215" s="11"/>
-      <c r="E215" s="11"/>
-      <c r="F215" s="11"/>
+      <c r="A215" s="7"/>
+      <c r="B215" s="7"/>
+      <c r="C215" s="7"/>
+      <c r="D215" s="7"/>
+      <c r="E215" s="7"/>
+      <c r="F215" s="7"/>
     </row>
     <row r="216" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="11"/>
-      <c r="B216" s="11"/>
-      <c r="C216" s="11"/>
-      <c r="D216" s="11"/>
-      <c r="E216" s="11"/>
-      <c r="F216" s="11"/>
+      <c r="A216" s="7"/>
+      <c r="B216" s="7"/>
+      <c r="C216" s="7"/>
+      <c r="D216" s="7"/>
+      <c r="E216" s="7"/>
+      <c r="F216" s="7"/>
     </row>
     <row r="217" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="11"/>
-      <c r="B217" s="11"/>
-      <c r="C217" s="11"/>
-      <c r="D217" s="11"/>
-      <c r="E217" s="11"/>
-      <c r="F217" s="11"/>
+      <c r="A217" s="7"/>
+      <c r="B217" s="7"/>
+      <c r="C217" s="7"/>
+      <c r="D217" s="7"/>
+      <c r="E217" s="7"/>
+      <c r="F217" s="7"/>
     </row>
     <row r="218" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="11"/>
-      <c r="B218" s="11"/>
-      <c r="C218" s="11"/>
-      <c r="D218" s="11"/>
-      <c r="E218" s="11"/>
-      <c r="F218" s="11"/>
+      <c r="A218" s="7"/>
+      <c r="B218" s="7"/>
+      <c r="C218" s="7"/>
+      <c r="D218" s="7"/>
+      <c r="E218" s="7"/>
+      <c r="F218" s="7"/>
     </row>
     <row r="219" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="11"/>
-      <c r="B219" s="11"/>
-      <c r="C219" s="11"/>
-      <c r="D219" s="11"/>
-      <c r="E219" s="11"/>
-      <c r="F219" s="11"/>
+      <c r="A219" s="7"/>
+      <c r="B219" s="7"/>
+      <c r="C219" s="7"/>
+      <c r="D219" s="7"/>
+      <c r="E219" s="7"/>
+      <c r="F219" s="7"/>
     </row>
     <row r="220" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="11"/>
-      <c r="B220" s="11"/>
-      <c r="C220" s="11"/>
-      <c r="D220" s="11"/>
-      <c r="E220" s="11"/>
-      <c r="F220" s="11"/>
+      <c r="A220" s="7"/>
+      <c r="B220" s="7"/>
+      <c r="C220" s="7"/>
+      <c r="D220" s="7"/>
+      <c r="E220" s="7"/>
+      <c r="F220" s="7"/>
     </row>
     <row r="221" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="11"/>
-      <c r="B221" s="11"/>
-      <c r="C221" s="11"/>
-      <c r="D221" s="11"/>
-      <c r="E221" s="11"/>
-      <c r="F221" s="11"/>
+      <c r="A221" s="7"/>
+      <c r="B221" s="7"/>
+      <c r="C221" s="7"/>
+      <c r="D221" s="7"/>
+      <c r="E221" s="7"/>
+      <c r="F221" s="7"/>
     </row>
     <row r="222" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="11"/>
-      <c r="B222" s="11"/>
-      <c r="C222" s="11"/>
-      <c r="D222" s="11"/>
-      <c r="E222" s="11"/>
-      <c r="F222" s="11"/>
+      <c r="A222" s="7"/>
+      <c r="B222" s="7"/>
+      <c r="C222" s="7"/>
+      <c r="D222" s="7"/>
+      <c r="E222" s="7"/>
+      <c r="F222" s="7"/>
     </row>
     <row r="223" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="11"/>
-      <c r="B223" s="11"/>
-      <c r="C223" s="11"/>
-      <c r="D223" s="11"/>
-      <c r="E223" s="11"/>
-      <c r="F223" s="11"/>
+      <c r="A223" s="7"/>
+      <c r="B223" s="7"/>
+      <c r="C223" s="7"/>
+      <c r="D223" s="7"/>
+      <c r="E223" s="7"/>
+      <c r="F223" s="7"/>
     </row>
     <row r="224" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="11"/>
-      <c r="B224" s="11"/>
-      <c r="C224" s="11"/>
-      <c r="D224" s="11"/>
-      <c r="E224" s="11"/>
-      <c r="F224" s="11"/>
+      <c r="A224" s="7"/>
+      <c r="B224" s="7"/>
+      <c r="C224" s="7"/>
+      <c r="D224" s="7"/>
+      <c r="E224" s="7"/>
+      <c r="F224" s="7"/>
     </row>
     <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
